--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_semiconductor.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_semiconductor.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="twse_6525" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,115 +590,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.06575</v>
+        <v>-0.0145</v>
+      </c>
+      <c r="E2">
+        <v>-0.02795</v>
+      </c>
+      <c r="F2">
+        <v>-0.00712</v>
       </c>
       <c r="G2">
-        <v>0.1120415224913495</v>
+        <v>0.5104163330664532</v>
       </c>
       <c r="H2">
-        <v>0.02749711649365629</v>
+        <v>0.3665092073658928</v>
       </c>
       <c r="I2">
-        <v>-0.09434832756632064</v>
+        <v>0.09393114491593274</v>
       </c>
       <c r="J2">
-        <v>-0.09434832756632064</v>
+        <v>0.08723915664962191</v>
       </c>
       <c r="K2">
-        <v>-28.18</v>
+        <v>30.92</v>
       </c>
       <c r="L2">
-        <v>-0.3250288350634371</v>
+        <v>0.04951160928742994</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.04102967625899281</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>4.721862871927555</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.02751236510791367</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>3.166235446313066</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>48.10000000000001</v>
+      </c>
+      <c r="T2">
+        <v>0.3294520547945206</v>
       </c>
       <c r="U2">
-        <v>34.17</v>
+        <v>298.86</v>
       </c>
       <c r="V2">
-        <v>0.1943686006825939</v>
+        <v>0.08398718525179856</v>
       </c>
       <c r="W2">
-        <v>-0.1652206747783612</v>
+        <v>-0.0589801520499366</v>
       </c>
       <c r="X2">
-        <v>0.2092638396986342</v>
+        <v>0.1344960729818899</v>
       </c>
       <c r="Y2">
-        <v>-0.3744845144769954</v>
+        <v>-0.1934762250318265</v>
       </c>
       <c r="Z2">
-        <v>0.546451531576957</v>
+        <v>1.12034013849521</v>
       </c>
       <c r="AA2">
-        <v>-0.05462023299064407</v>
+        <v>0.04139522329437216</v>
       </c>
       <c r="AB2">
-        <v>0.161185260240099</v>
+        <v>0.1301162760970662</v>
       </c>
       <c r="AC2">
-        <v>-0.2158054932307431</v>
+        <v>-0.08870351570075419</v>
       </c>
       <c r="AD2">
-        <v>43.1</v>
+        <v>46.15</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>43.1</v>
+        <v>46.15</v>
       </c>
       <c r="AG2">
-        <v>8.93</v>
+        <v>-252.71</v>
       </c>
       <c r="AH2">
-        <v>0.1968935587026039</v>
+        <v>0.0128032625431746</v>
       </c>
       <c r="AI2">
-        <v>0.2097323600973236</v>
+        <v>0.04981380538615144</v>
       </c>
       <c r="AJ2">
-        <v>0.04834082173983652</v>
+        <v>-0.07644697476169877</v>
       </c>
       <c r="AK2">
-        <v>0.0521216366077161</v>
+        <v>-0.4026673465160376</v>
       </c>
       <c r="AL2">
-        <v>1.46</v>
+        <v>1.767</v>
       </c>
       <c r="AM2">
-        <v>1.35</v>
+        <v>-5.44</v>
       </c>
       <c r="AN2">
-        <v>-27.27848101265823</v>
+        <v>0.4563884493670886</v>
       </c>
       <c r="AO2">
-        <v>-5.602739726027397</v>
+        <v>33.19750990379174</v>
       </c>
       <c r="AP2">
-        <v>-5.651898734177215</v>
+        <v>-2.499109968354431</v>
       </c>
       <c r="AQ2">
-        <v>-6.059259259259259</v>
+        <v>-10.78308823529412</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +718,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GCS Holdings, Inc. (TPEX:4991)</t>
+          <t>GEM Services, Inc. (TWSE:6525)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,115 +727,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.06660000000000001</v>
+        <v>0.0567</v>
+      </c>
+      <c r="E3">
+        <v>-0.0712</v>
       </c>
       <c r="G3">
-        <v>0.194320987654321</v>
+        <v>0.3323741007194244</v>
       </c>
       <c r="H3">
-        <v>0.06765432098765432</v>
+        <v>0.3223021582733813</v>
       </c>
       <c r="I3">
-        <v>-0.05604938271604938</v>
+        <v>0.1424460431654676</v>
       </c>
       <c r="J3">
-        <v>-0.05604938271604938</v>
+        <v>0.1146072730856411</v>
       </c>
       <c r="K3">
-        <v>-22.2</v>
+        <v>17.6</v>
       </c>
       <c r="L3">
-        <v>-0.5481481481481482</v>
+        <v>0.1266187050359712</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>22.1</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.07670947587643179</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.255681818181818</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>22.1</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.07670947587643179</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.255681818181818</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>25.9</v>
+        <v>46.5</v>
       </c>
       <c r="V3">
-        <v>0.1840796019900497</v>
+        <v>0.1614022908712253</v>
       </c>
       <c r="W3">
-        <v>-0.1903945111492281</v>
+        <v>0.1311475409836066</v>
       </c>
       <c r="X3">
-        <v>0.1666221749961896</v>
+        <v>0.1299205397935869</v>
       </c>
       <c r="Y3">
-        <v>-0.3570166861454178</v>
+        <v>0.001227001190019728</v>
       </c>
       <c r="Z3">
-        <v>0.4613807245386193</v>
+        <v>1.672884823685161</v>
       </c>
       <c r="AA3">
-        <v>-0.02586010480747323</v>
+        <v>0.1917247678289098</v>
       </c>
       <c r="AB3">
-        <v>0.1565533961507093</v>
+        <v>0.129536272346502</v>
       </c>
       <c r="AC3">
-        <v>-0.1824135009581826</v>
+        <v>0.06218849548240782</v>
       </c>
       <c r="AD3">
-        <v>13.9</v>
+        <v>1.42</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>13.9</v>
+        <v>1.42</v>
       </c>
       <c r="AG3">
-        <v>-12</v>
+        <v>-45.08</v>
       </c>
       <c r="AH3">
-        <v>0.08990944372574386</v>
+        <v>0.004904669798286819</v>
       </c>
       <c r="AI3">
-        <v>0.09733893557422969</v>
+        <v>0.01091300338149401</v>
       </c>
       <c r="AJ3">
-        <v>-0.09324009324009323</v>
+        <v>-0.1854991358735906</v>
       </c>
       <c r="AK3">
-        <v>-0.1026518391787853</v>
+        <v>-0.5391054771585746</v>
       </c>
       <c r="AL3">
-        <v>0.31</v>
+        <v>0.076</v>
       </c>
       <c r="AM3">
-        <v>0.215</v>
+        <v>-1.104</v>
       </c>
       <c r="AN3">
-        <v>11.48760330578513</v>
+        <v>0.0370757180156658</v>
       </c>
       <c r="AO3">
-        <v>-7.32258064516129</v>
+        <v>260.5263157894737</v>
       </c>
       <c r="AP3">
-        <v>-9.917355371900825</v>
+        <v>-1.177023498694517</v>
       </c>
       <c r="AQ3">
-        <v>-10.55813953488372</v>
+        <v>-17.93478260869566</v>
       </c>
     </row>
     <row r="4">
@@ -835,124 +852,9158 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Parade Technologies, Ltd. (TPEX:4966)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Semiconductor</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0581</v>
+      </c>
+      <c r="E4">
+        <v>0.0153</v>
+      </c>
+      <c r="F4">
+        <v>-0.00712</v>
+      </c>
+      <c r="G4">
+        <v>0.6572689384653102</v>
+      </c>
+      <c r="H4">
+        <v>0.4628585437607257</v>
+      </c>
+      <c r="I4">
+        <v>0.1367982348614857</v>
+      </c>
+      <c r="J4">
+        <v>0.1245492645450452</v>
+      </c>
+      <c r="K4">
+        <v>57.4</v>
+      </c>
+      <c r="L4">
+        <v>0.1407207648933562</v>
+      </c>
+      <c r="M4">
+        <v>123.9</v>
+      </c>
+      <c r="N4">
+        <v>0.03976251604621309</v>
+      </c>
+      <c r="O4">
+        <v>2.158536585365854</v>
+      </c>
+      <c r="P4">
+        <v>75.8</v>
+      </c>
+      <c r="Q4">
+        <v>0.02432605905006418</v>
+      </c>
+      <c r="R4">
+        <v>1.320557491289199</v>
+      </c>
+      <c r="S4">
+        <v>48.10000000000001</v>
+      </c>
+      <c r="T4">
+        <v>0.3882163034705408</v>
+      </c>
+      <c r="U4">
+        <v>240.8</v>
+      </c>
+      <c r="V4">
+        <v>0.07727856225930681</v>
+      </c>
+      <c r="W4">
+        <v>0.0864718288641157</v>
+      </c>
+      <c r="X4">
+        <v>0.1296083536974164</v>
+      </c>
+      <c r="Y4">
+        <v>-0.04313652483330066</v>
+      </c>
+      <c r="Z4">
+        <v>1.361572868682823</v>
+      </c>
+      <c r="AA4">
+        <v>0.169582899418933</v>
+      </c>
+      <c r="AB4">
+        <v>0.1295011981426224</v>
+      </c>
+      <c r="AC4">
+        <v>0.04008170127631064</v>
+      </c>
+      <c r="AD4">
+        <v>4.63</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>4.63</v>
+      </c>
+      <c r="AG4">
+        <v>-236.17</v>
+      </c>
+      <c r="AH4">
+        <v>0.001483674770799486</v>
+      </c>
+      <c r="AI4">
+        <v>0.007303645512911521</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.08200831299069737</v>
+      </c>
+      <c r="AK4">
+        <v>-0.6007427568488797</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>-5.89</v>
+      </c>
+      <c r="AN4">
+        <v>0.06333789329685363</v>
+      </c>
+      <c r="AP4">
+        <v>-3.23077975376197</v>
+      </c>
+      <c r="AQ4">
+        <v>-9.473684210526315</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GCS Holdings, Inc. (TPEX:4991)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Semiconductor</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>-0.0857</v>
+      </c>
+      <c r="G5">
+        <v>0.1698275862068965</v>
+      </c>
+      <c r="H5">
+        <v>-0.01637931034482759</v>
+      </c>
+      <c r="I5">
+        <v>-0.2435960591133005</v>
+      </c>
+      <c r="J5">
+        <v>-0.2435960591133005</v>
+      </c>
+      <c r="K5">
+        <v>-36.7</v>
+      </c>
+      <c r="L5">
+        <v>-0.9039408866995075</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>7.19</v>
+      </c>
+      <c r="V5">
+        <v>0.06187607573149742</v>
+      </c>
+      <c r="W5">
+        <v>-0.2847168347556245</v>
+      </c>
+      <c r="X5">
+        <v>0.1390716061701929</v>
+      </c>
+      <c r="Y5">
+        <v>-0.4237884409258174</v>
+      </c>
+      <c r="Z5">
+        <v>0.3562966213251426</v>
+      </c>
+      <c r="AA5">
+        <v>-0.08679245283018869</v>
+      </c>
+      <c r="AB5">
+        <v>0.1306962798476303</v>
+      </c>
+      <c r="AC5">
+        <v>-0.217488732677819</v>
+      </c>
+      <c r="AD5">
+        <v>12.3</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>12.3</v>
+      </c>
+      <c r="AG5">
+        <v>5.11</v>
+      </c>
+      <c r="AH5">
+        <v>0.09571984435797666</v>
+      </c>
+      <c r="AI5">
+        <v>0.1121239744758432</v>
+      </c>
+      <c r="AJ5">
+        <v>0.04212348528563185</v>
+      </c>
+      <c r="AK5">
+        <v>0.04984879523948883</v>
+      </c>
+      <c r="AL5">
+        <v>0.531</v>
+      </c>
+      <c r="AM5">
+        <v>0.421</v>
+      </c>
+      <c r="AN5">
+        <v>-2.060301507537689</v>
+      </c>
+      <c r="AO5">
+        <v>-18.62523540489642</v>
+      </c>
+      <c r="AP5">
+        <v>-0.8559463986599666</v>
+      </c>
+      <c r="AQ5">
+        <v>-23.4916864608076</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>HY Electronic (Cayman) Limited (TWSE:6573)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Semiconductor</t>
         </is>
       </c>
+      <c r="D6">
+        <v>-0.114</v>
+      </c>
+      <c r="G6">
+        <v>-0.06594594594594594</v>
+      </c>
+      <c r="H6">
+        <v>-0.1094594594594595</v>
+      </c>
+      <c r="I6">
+        <v>-0.1905405405405405</v>
+      </c>
+      <c r="J6">
+        <v>-0.1905405405405405</v>
+      </c>
+      <c r="K6">
+        <v>-7.38</v>
+      </c>
+      <c r="L6">
+        <v>-0.1994594594594594</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>4.37</v>
+      </c>
+      <c r="V6">
+        <v>0.1146981627296588</v>
+      </c>
+      <c r="W6">
+        <v>-0.2044321329639889</v>
+      </c>
+      <c r="X6">
+        <v>0.195634430380168</v>
+      </c>
+      <c r="Y6">
+        <v>-0.4000665633441569</v>
+      </c>
+      <c r="Z6">
+        <v>0.6085526315789473</v>
+      </c>
+      <c r="AA6">
+        <v>-0.1159539473684211</v>
+      </c>
+      <c r="AB6">
+        <v>0.1348620475724536</v>
+      </c>
+      <c r="AC6">
+        <v>-0.2508159949408747</v>
+      </c>
+      <c r="AD6">
+        <v>27.8</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>27.8</v>
+      </c>
+      <c r="AG6">
+        <v>23.43</v>
+      </c>
+      <c r="AH6">
+        <v>0.4218512898330804</v>
+      </c>
+      <c r="AI6">
+        <v>0.5275142314990512</v>
+      </c>
+      <c r="AJ6">
+        <v>0.3807898586055583</v>
+      </c>
+      <c r="AK6">
+        <v>0.4847920546244568</v>
+      </c>
+      <c r="AL6">
+        <v>1.16</v>
+      </c>
+      <c r="AM6">
+        <v>1.133</v>
+      </c>
+      <c r="AN6">
+        <v>-6.450116009280743</v>
+      </c>
+      <c r="AO6">
+        <v>-6.077586206896552</v>
+      </c>
+      <c r="AP6">
+        <v>-5.436194895591647</v>
+      </c>
+      <c r="AQ6">
+        <v>-6.222418358340688</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GEM Services, Inc. (TWSE:6525)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TWSE:6525</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Semiconductor</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>260.526315789474</v>
+      </c>
+      <c r="F2">
+        <v>10000000</v>
+      </c>
+      <c r="G2">
+        <v>0.0370757180156658</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0.00490466979828682</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>288.1</v>
+      </c>
+      <c r="L2">
+        <v>289.68790869812</v>
+      </c>
+      <c r="M2">
+        <v>243.02</v>
+      </c>
+      <c r="N2">
+        <v>243.18790869812</v>
+      </c>
+      <c r="O2">
+        <v>1.42</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0.129536272346502</v>
+      </c>
+      <c r="R2">
+        <v>0.129473623634058</v>
+      </c>
+      <c r="S2">
+        <v>0.0515732783287875</v>
+      </c>
+      <c r="T2">
+        <v>0.0447</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.129920539793587</v>
+      </c>
+      <c r="X2">
+        <v>0.129473623634058</v>
+      </c>
+      <c r="Y2">
+        <v>1.66380055146922</v>
+      </c>
+      <c r="Z2">
+        <v>1.65564015915405</v>
+      </c>
+      <c r="AA2">
+        <v>1.42</v>
+      </c>
+      <c r="AB2">
+        <v>0.0515732783287875</v>
+      </c>
+      <c r="AC2">
+        <v>260.5263157894737</v>
+      </c>
+      <c r="AD2">
+        <v>1.42</v>
+      </c>
+      <c r="AE2">
+        <v>0.076</v>
+      </c>
+      <c r="AF2">
+        <v>18.5</v>
+      </c>
+      <c r="AG2">
+        <v>38.3</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>288.1</v>
+      </c>
+      <c r="AK2">
+        <v>0.05476650414205181</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>38.49999999999999</v>
+      </c>
+      <c r="AR2">
+        <v>0.076</v>
+      </c>
+      <c r="AS2">
+        <v>1.42</v>
+      </c>
+      <c r="AT2">
+        <v>46.5</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1294736236340577</v>
+      </c>
+      <c r="C2">
+        <v>289.68790869812</v>
+      </c>
+      <c r="D2">
+        <v>243.18790869812</v>
+      </c>
+      <c r="E2">
+        <v>-1.42</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>46.5</v>
+      </c>
+      <c r="H2">
+        <v>288.1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>38.3</v>
+      </c>
+      <c r="K2">
+        <v>18.5</v>
+      </c>
+      <c r="L2">
+        <v>19.8</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>19.8</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>19.8</v>
+      </c>
+      <c r="Q2">
+        <v>38.3</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1294736236340577</v>
+      </c>
+      <c r="T2">
+        <v>1.655640159154051</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0.0447</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1295326236340577</v>
+      </c>
+      <c r="C3">
+        <v>286.6345727814175</v>
+      </c>
+      <c r="D3">
+        <v>243.0297727814175</v>
+      </c>
+      <c r="E3">
+        <v>1.475200000000001</v>
+      </c>
+      <c r="F3">
+        <v>2.8952</v>
+      </c>
+      <c r="G3">
+        <v>46.5</v>
+      </c>
+      <c r="H3">
+        <v>288.1</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>38.3</v>
+      </c>
+      <c r="K3">
+        <v>18.5</v>
+      </c>
+      <c r="L3">
+        <v>19.8</v>
+      </c>
+      <c r="M3">
+        <v>0.12941544</v>
+      </c>
+      <c r="N3">
+        <v>19.67058456</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>19.67058456</v>
+      </c>
+      <c r="Q3">
+        <v>38.17058455999999</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1303895188222805</v>
+      </c>
+      <c r="T3">
+        <v>1.672363797125305</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0.0447</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>152.9956549234002</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1295916236340577</v>
+      </c>
+      <c r="C4">
+        <v>283.5814423907033</v>
+      </c>
       <c r="D4">
-        <v>-0.0649</v>
+        <v>242.8718423907033</v>
+      </c>
+      <c r="E4">
+        <v>4.370400000000001</v>
+      </c>
+      <c r="F4">
+        <v>5.790400000000001</v>
       </c>
       <c r="G4">
-        <v>0.03991341991341991</v>
+        <v>46.5</v>
       </c>
       <c r="H4">
-        <v>-0.007705627705627705</v>
+        <v>288.1</v>
       </c>
       <c r="I4">
-        <v>-0.1279220779220779</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>-0.1279220779220779</v>
+        <v>38.3</v>
       </c>
       <c r="K4">
-        <v>-5.98</v>
+        <v>18.5</v>
       </c>
       <c r="L4">
-        <v>-0.1294372294372294</v>
+        <v>19.8</v>
       </c>
       <c r="M4">
+        <v>0.25883088</v>
+      </c>
+      <c r="N4">
+        <v>19.54116912</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>19.54116912</v>
+      </c>
+      <c r="Q4">
+        <v>38.04116911999999</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1313241057490385</v>
+      </c>
+      <c r="T4">
+        <v>1.689428733830665</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0.0447</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>76.49782746170007</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1296506236340577</v>
+      </c>
+      <c r="C5">
+        <v>280.5285171255607</v>
+      </c>
+      <c r="D5">
+        <v>242.7141171255607</v>
+      </c>
+      <c r="E5">
+        <v>7.265600000000001</v>
+      </c>
+      <c r="F5">
+        <v>8.685600000000001</v>
+      </c>
+      <c r="G5">
+        <v>46.5</v>
+      </c>
+      <c r="H5">
+        <v>288.1</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>38.3</v>
+      </c>
+      <c r="K5">
+        <v>18.5</v>
+      </c>
+      <c r="L5">
+        <v>19.8</v>
+      </c>
+      <c r="M5">
+        <v>0.3882463200000001</v>
+      </c>
+      <c r="N5">
+        <v>19.41175368</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>19.41175368</v>
+      </c>
+      <c r="Q5">
+        <v>37.91175368</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1322779625093378</v>
+      </c>
+      <c r="T5">
+        <v>1.706845524901084</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0.0447</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>50.99855164113338</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1297096236340577</v>
+      </c>
+      <c r="C6">
+        <v>277.4757965866126</v>
+      </c>
+      <c r="D6">
+        <v>242.5565965866126</v>
+      </c>
+      <c r="E6">
+        <v>10.1608</v>
+      </c>
+      <c r="F6">
+        <v>11.5808</v>
+      </c>
+      <c r="G6">
+        <v>46.5</v>
+      </c>
+      <c r="H6">
+        <v>288.1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>38.3</v>
+      </c>
+      <c r="K6">
+        <v>18.5</v>
+      </c>
+      <c r="L6">
+        <v>19.8</v>
+      </c>
+      <c r="M6">
+        <v>0.5176617600000001</v>
+      </c>
+      <c r="N6">
+        <v>19.28233824</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>19.28233824</v>
+      </c>
+      <c r="Q6">
+        <v>37.78233824</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1332516912854768</v>
+      </c>
+      <c r="T6">
+        <v>1.724625165785471</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0.0447</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>38.24891373085004</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1297686236340576</v>
+      </c>
+      <c r="C7">
+        <v>274.423280375518</v>
+      </c>
+      <c r="D7">
+        <v>242.399280375518</v>
+      </c>
+      <c r="E7">
+        <v>13.056</v>
+      </c>
+      <c r="F7">
+        <v>14.476</v>
+      </c>
+      <c r="G7">
+        <v>46.5</v>
+      </c>
+      <c r="H7">
+        <v>288.1</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>38.3</v>
+      </c>
+      <c r="K7">
+        <v>18.5</v>
+      </c>
+      <c r="L7">
+        <v>19.8</v>
+      </c>
+      <c r="M7">
+        <v>0.6470772000000001</v>
+      </c>
+      <c r="N7">
+        <v>19.1529228</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>19.1529228</v>
+      </c>
+      <c r="Q7">
+        <v>37.6529228</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1342459196147975</v>
+      </c>
+      <c r="T7">
+        <v>1.742779114899002</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0.0447</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>30.59913098468003</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1298276236340577</v>
+      </c>
+      <c r="C8">
+        <v>271.3709680949684</v>
+      </c>
+      <c r="D8">
+        <v>242.2421680949684</v>
+      </c>
+      <c r="E8">
+        <v>15.9512</v>
+      </c>
+      <c r="F8">
+        <v>17.3712</v>
+      </c>
+      <c r="G8">
+        <v>46.5</v>
+      </c>
+      <c r="H8">
+        <v>288.1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>38.3</v>
+      </c>
+      <c r="K8">
+        <v>18.5</v>
+      </c>
+      <c r="L8">
+        <v>19.8</v>
+      </c>
+      <c r="M8">
+        <v>0.7764926400000002</v>
+      </c>
+      <c r="N8">
+        <v>19.02350736</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>19.02350736</v>
+      </c>
+      <c r="Q8">
+        <v>37.52350736</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1352613017383592</v>
+      </c>
+      <c r="T8">
+        <v>1.761319318248991</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0.0447</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>25.49927582056669</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1298866236340576</v>
+      </c>
+      <c r="C9">
+        <v>268.3188593486851</v>
+      </c>
+      <c r="D9">
+        <v>242.0852593486851</v>
+      </c>
+      <c r="E9">
+        <v>18.8464</v>
+      </c>
+      <c r="F9">
+        <v>20.2664</v>
+      </c>
+      <c r="G9">
+        <v>46.5</v>
+      </c>
+      <c r="H9">
+        <v>288.1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>38.3</v>
+      </c>
+      <c r="K9">
+        <v>18.5</v>
+      </c>
+      <c r="L9">
+        <v>19.8</v>
+      </c>
+      <c r="M9">
+        <v>0.9059080800000002</v>
+      </c>
+      <c r="N9">
+        <v>18.89409192</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>18.89409192</v>
+      </c>
+      <c r="Q9">
+        <v>37.39409191999999</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1362985200366211</v>
+      </c>
+      <c r="T9">
+        <v>1.780258235649518</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0.0447</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>21.85652213191431</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1299456236340577</v>
+      </c>
+      <c r="C10">
+        <v>265.266953741415</v>
+      </c>
+      <c r="D10">
+        <v>241.928553741415</v>
+      </c>
+      <c r="E10">
+        <v>21.74160000000001</v>
+      </c>
+      <c r="F10">
+        <v>23.1616</v>
+      </c>
+      <c r="G10">
+        <v>46.5</v>
+      </c>
+      <c r="H10">
+        <v>288.1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>38.3</v>
+      </c>
+      <c r="K10">
+        <v>18.5</v>
+      </c>
+      <c r="L10">
+        <v>19.8</v>
+      </c>
+      <c r="M10">
+        <v>1.03532352</v>
+      </c>
+      <c r="N10">
+        <v>18.76467648</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>18.76467648</v>
+      </c>
+      <c r="Q10">
+        <v>37.26467648</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1373582865587583</v>
+      </c>
+      <c r="T10">
+        <v>1.799608868645708</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0.0447</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>19.12445686542502</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1300046236340577</v>
+      </c>
+      <c r="C11">
+        <v>262.2152508789284</v>
+      </c>
+      <c r="D11">
+        <v>241.7720508789284</v>
+      </c>
+      <c r="E11">
+        <v>24.6368</v>
+      </c>
+      <c r="F11">
+        <v>26.0568</v>
+      </c>
+      <c r="G11">
+        <v>46.5</v>
+      </c>
+      <c r="H11">
+        <v>288.1</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>38.3</v>
+      </c>
+      <c r="K11">
+        <v>18.5</v>
+      </c>
+      <c r="L11">
+        <v>19.8</v>
+      </c>
+      <c r="M11">
+        <v>1.16473896</v>
+      </c>
+      <c r="N11">
+        <v>18.63526104</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>18.63526104</v>
+      </c>
+      <c r="Q11">
+        <v>37.13526104</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1384413446528106</v>
+      </c>
+      <c r="T11">
+        <v>1.819384790279178</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0.0447</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>16.99951721371113</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1300636236340577</v>
+      </c>
+      <c r="C12">
+        <v>259.1637503680146</v>
+      </c>
+      <c r="D12">
+        <v>241.6157503680145</v>
+      </c>
+      <c r="E12">
+        <v>27.532</v>
+      </c>
+      <c r="F12">
+        <v>28.95200000000001</v>
+      </c>
+      <c r="G12">
+        <v>46.5</v>
+      </c>
+      <c r="H12">
+        <v>288.1</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>38.3</v>
+      </c>
+      <c r="K12">
+        <v>18.5</v>
+      </c>
+      <c r="L12">
+        <v>19.8</v>
+      </c>
+      <c r="M12">
+        <v>1.2941544</v>
+      </c>
+      <c r="N12">
+        <v>18.5058456</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>18.5058456</v>
+      </c>
+      <c r="Q12">
+        <v>37.0058456</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1395484707045085</v>
+      </c>
+      <c r="T12">
+        <v>1.839600176837835</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0.0447</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>15.29956549234002</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1301226236340577</v>
+      </c>
+      <c r="C13">
+        <v>256.1124518164789</v>
+      </c>
+      <c r="D13">
+        <v>241.4596518164789</v>
+      </c>
+      <c r="E13">
+        <v>30.42720000000001</v>
+      </c>
+      <c r="F13">
+        <v>31.8472</v>
+      </c>
+      <c r="G13">
+        <v>46.5</v>
+      </c>
+      <c r="H13">
+        <v>288.1</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>38.3</v>
+      </c>
+      <c r="K13">
+        <v>18.5</v>
+      </c>
+      <c r="L13">
+        <v>19.8</v>
+      </c>
+      <c r="M13">
+        <v>1.42356984</v>
+      </c>
+      <c r="N13">
+        <v>18.37643016</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>18.37643016</v>
+      </c>
+      <c r="Q13">
+        <v>36.87643016</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1406804759933232</v>
+      </c>
+      <c r="T13">
+        <v>1.860269841746125</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0.0447</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>13.90869590212729</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1303136236340577</v>
+      </c>
+      <c r="C14">
+        <v>252.7132963214877</v>
+      </c>
+      <c r="D14">
+        <v>240.9556963214877</v>
+      </c>
+      <c r="E14">
+        <v>33.3224</v>
+      </c>
+      <c r="F14">
+        <v>34.7424</v>
+      </c>
+      <c r="G14">
+        <v>46.5</v>
+      </c>
+      <c r="H14">
+        <v>288.1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>38.3</v>
+      </c>
+      <c r="K14">
+        <v>18.5</v>
+      </c>
+      <c r="L14">
+        <v>19.8</v>
+      </c>
+      <c r="M14">
+        <v>1.59120192</v>
+      </c>
+      <c r="N14">
+        <v>18.20879808</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>18.20879808</v>
+      </c>
+      <c r="Q14">
+        <v>36.70879807999999</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1418382086750655</v>
+      </c>
+      <c r="T14">
+        <v>1.881409271765967</v>
+      </c>
+      <c r="U14">
+        <v>0.0458</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0.0458</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>12.44342389933768</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1303836236340577</v>
+      </c>
+      <c r="C15">
+        <v>249.6339269462956</v>
+      </c>
+      <c r="D15">
+        <v>240.7715269462956</v>
+      </c>
+      <c r="E15">
+        <v>36.2176</v>
+      </c>
+      <c r="F15">
+        <v>37.63760000000001</v>
+      </c>
+      <c r="G15">
+        <v>46.5</v>
+      </c>
+      <c r="H15">
+        <v>288.1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>38.3</v>
+      </c>
+      <c r="K15">
+        <v>18.5</v>
+      </c>
+      <c r="L15">
+        <v>19.8</v>
+      </c>
+      <c r="M15">
+        <v>1.72380208</v>
+      </c>
+      <c r="N15">
+        <v>18.07619792</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>18.07619792</v>
+      </c>
+      <c r="Q15">
+        <v>36.57619792</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1430225559012157</v>
+      </c>
+      <c r="T15">
+        <v>1.903034665694312</v>
+      </c>
+      <c r="U15">
+        <v>0.0458</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0.0458</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>11.48623744554247</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1304536236340577</v>
+      </c>
+      <c r="C16">
+        <v>246.5548388879955</v>
+      </c>
+      <c r="D16">
+        <v>240.5876388879955</v>
+      </c>
+      <c r="E16">
+        <v>39.11280000000001</v>
+      </c>
+      <c r="F16">
+        <v>40.53280000000001</v>
+      </c>
+      <c r="G16">
+        <v>46.5</v>
+      </c>
+      <c r="H16">
+        <v>288.1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>38.3</v>
+      </c>
+      <c r="K16">
+        <v>18.5</v>
+      </c>
+      <c r="L16">
+        <v>19.8</v>
+      </c>
+      <c r="M16">
+        <v>1.85640224</v>
+      </c>
+      <c r="N16">
+        <v>17.94359776</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>17.94359776</v>
+      </c>
+      <c r="Q16">
+        <v>36.44359776</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1442344460861136</v>
+      </c>
+      <c r="T16">
+        <v>1.925162975760525</v>
+      </c>
+      <c r="U16">
+        <v>0.0458</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0.0458</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>10.66579191371801</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1308536236340577</v>
+      </c>
+      <c r="C17">
+        <v>242.6142150170378</v>
+      </c>
+      <c r="D17">
+        <v>239.5422150170378</v>
+      </c>
+      <c r="E17">
+        <v>42.008</v>
+      </c>
+      <c r="F17">
+        <v>43.428</v>
+      </c>
+      <c r="G17">
+        <v>46.5</v>
+      </c>
+      <c r="H17">
+        <v>288.1</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>38.3</v>
+      </c>
+      <c r="K17">
+        <v>18.5</v>
+      </c>
+      <c r="L17">
+        <v>19.8</v>
+      </c>
+      <c r="M17">
+        <v>2.084544</v>
+      </c>
+      <c r="N17">
+        <v>17.715456</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>17.715456</v>
+      </c>
+      <c r="Q17">
+        <v>36.215456</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1454748513341855</v>
+      </c>
+      <c r="T17">
+        <v>1.947811951945943</v>
+      </c>
+      <c r="U17">
+        <v>0.048</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0.048</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>9.498480243161094</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1309456236340577</v>
+      </c>
+      <c r="C18">
+        <v>239.4798513659339</v>
+      </c>
+      <c r="D18">
+        <v>239.3030513659339</v>
+      </c>
+      <c r="E18">
+        <v>44.90320000000001</v>
+      </c>
+      <c r="F18">
+        <v>46.32320000000001</v>
+      </c>
+      <c r="G18">
+        <v>46.5</v>
+      </c>
+      <c r="H18">
+        <v>288.1</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>38.3</v>
+      </c>
+      <c r="K18">
+        <v>18.5</v>
+      </c>
+      <c r="L18">
+        <v>19.8</v>
+      </c>
+      <c r="M18">
+        <v>2.2235136</v>
+      </c>
+      <c r="N18">
+        <v>17.5764864</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>17.5764864</v>
+      </c>
+      <c r="Q18">
+        <v>36.07648639999999</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1467447900405449</v>
+      </c>
+      <c r="T18">
+        <v>1.971000189469109</v>
+      </c>
+      <c r="U18">
+        <v>0.048</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0.048</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>8.904825227963524</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1310376236340577</v>
+      </c>
+      <c r="C19">
+        <v>236.3459648098599</v>
+      </c>
+      <c r="D19">
+        <v>239.0643648098599</v>
+      </c>
+      <c r="E19">
+        <v>47.79840000000001</v>
+      </c>
+      <c r="F19">
+        <v>49.21840000000001</v>
+      </c>
+      <c r="G19">
+        <v>46.5</v>
+      </c>
+      <c r="H19">
+        <v>288.1</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>38.3</v>
+      </c>
+      <c r="K19">
+        <v>18.5</v>
+      </c>
+      <c r="L19">
+        <v>19.8</v>
+      </c>
+      <c r="M19">
+        <v>2.362483200000001</v>
+      </c>
+      <c r="N19">
+        <v>17.4375168</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>17.4375168</v>
+      </c>
+      <c r="Q19">
+        <v>35.9375168</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1480453296795876</v>
+      </c>
+      <c r="T19">
+        <v>1.994747179703677</v>
+      </c>
+      <c r="U19">
+        <v>0.048</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0.048</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>8.381011979259787</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1311296236340577</v>
+      </c>
+      <c r="C20">
+        <v>233.2125539226403</v>
+      </c>
+      <c r="D20">
+        <v>238.8261539226403</v>
+      </c>
+      <c r="E20">
+        <v>50.6936</v>
+      </c>
+      <c r="F20">
+        <v>52.11360000000001</v>
+      </c>
+      <c r="G20">
+        <v>46.5</v>
+      </c>
+      <c r="H20">
+        <v>288.1</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>38.3</v>
+      </c>
+      <c r="K20">
+        <v>18.5</v>
+      </c>
+      <c r="L20">
+        <v>19.8</v>
+      </c>
+      <c r="M20">
+        <v>2.5014528</v>
+      </c>
+      <c r="N20">
+        <v>17.2985472</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>17.2985472</v>
+      </c>
+      <c r="Q20">
+        <v>35.7985472</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1493775897976313</v>
+      </c>
+      <c r="T20">
+        <v>2.019073364822014</v>
+      </c>
+      <c r="U20">
+        <v>0.048</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0.048</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>7.915400202634244</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1315066236340577</v>
+      </c>
+      <c r="C21">
+        <v>229.3461454318183</v>
+      </c>
+      <c r="D21">
+        <v>237.8549454318184</v>
+      </c>
+      <c r="E21">
+        <v>53.58880000000001</v>
+      </c>
+      <c r="F21">
+        <v>55.00880000000001</v>
+      </c>
+      <c r="G21">
+        <v>46.5</v>
+      </c>
+      <c r="H21">
+        <v>288.1</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>38.3</v>
+      </c>
+      <c r="K21">
+        <v>18.5</v>
+      </c>
+      <c r="L21">
+        <v>19.8</v>
+      </c>
+      <c r="M21">
+        <v>2.7229356</v>
+      </c>
+      <c r="N21">
+        <v>17.0770644</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>17.0770644</v>
+      </c>
+      <c r="Q21">
+        <v>35.5770644</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1507427452272317</v>
+      </c>
+      <c r="T21">
+        <v>2.044000196486483</v>
+      </c>
+      <c r="U21">
+        <v>0.0495</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0.0495</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>7.271563822515669</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1316136236340577</v>
+      </c>
+      <c r="C22">
+        <v>226.1767348346592</v>
+      </c>
+      <c r="D22">
+        <v>237.5807348346592</v>
+      </c>
+      <c r="E22">
+        <v>56.48400000000001</v>
+      </c>
+      <c r="F22">
+        <v>57.90400000000001</v>
+      </c>
+      <c r="G22">
+        <v>46.5</v>
+      </c>
+      <c r="H22">
+        <v>288.1</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>38.3</v>
+      </c>
+      <c r="K22">
+        <v>18.5</v>
+      </c>
+      <c r="L22">
+        <v>19.8</v>
+      </c>
+      <c r="M22">
+        <v>2.866248000000001</v>
+      </c>
+      <c r="N22">
+        <v>16.933752</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>16.933752</v>
+      </c>
+      <c r="Q22">
+        <v>35.433752</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1521420295425721</v>
+      </c>
+      <c r="T22">
+        <v>2.069550198942564</v>
+      </c>
+      <c r="U22">
+        <v>0.0495</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0.0495</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>6.907985631389885</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1317206236340577</v>
+      </c>
+      <c r="C23">
+        <v>223.0079557557301</v>
+      </c>
+      <c r="D23">
+        <v>237.3071557557302</v>
+      </c>
+      <c r="E23">
+        <v>59.3792</v>
+      </c>
+      <c r="F23">
+        <v>60.79920000000001</v>
+      </c>
+      <c r="G23">
+        <v>46.5</v>
+      </c>
+      <c r="H23">
+        <v>288.1</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>38.3</v>
+      </c>
+      <c r="K23">
+        <v>18.5</v>
+      </c>
+      <c r="L23">
+        <v>19.8</v>
+      </c>
+      <c r="M23">
+        <v>3.0095604</v>
+      </c>
+      <c r="N23">
+        <v>16.7904396</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>16.7904396</v>
+      </c>
+      <c r="Q23">
+        <v>35.2904396</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1535767387772882</v>
+      </c>
+      <c r="T23">
+        <v>2.095747036903863</v>
+      </c>
+      <c r="U23">
+        <v>0.0495</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0.0495</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>6.579033934657034</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1318276236340577</v>
+      </c>
+      <c r="C24">
+        <v>219.8398060159223</v>
+      </c>
+      <c r="D24">
+        <v>237.0342060159223</v>
+      </c>
+      <c r="E24">
+        <v>62.27440000000001</v>
+      </c>
+      <c r="F24">
+        <v>63.69440000000001</v>
+      </c>
+      <c r="G24">
+        <v>46.5</v>
+      </c>
+      <c r="H24">
+        <v>288.1</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>38.3</v>
+      </c>
+      <c r="K24">
+        <v>18.5</v>
+      </c>
+      <c r="L24">
+        <v>19.8</v>
+      </c>
+      <c r="M24">
+        <v>3.1528728</v>
+      </c>
+      <c r="N24">
+        <v>16.6471272</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>16.6471272</v>
+      </c>
+      <c r="Q24">
+        <v>35.1471272</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1550482354282791</v>
+      </c>
+      <c r="T24">
+        <v>2.12261558865904</v>
+      </c>
+      <c r="U24">
+        <v>0.0495</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0.0495</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>6.279986937627169</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1322566236340577</v>
+      </c>
+      <c r="C25">
+        <v>215.8565325287075</v>
+      </c>
+      <c r="D25">
+        <v>235.9461325287075</v>
+      </c>
+      <c r="E25">
+        <v>65.16960000000002</v>
+      </c>
+      <c r="F25">
+        <v>66.58960000000002</v>
+      </c>
+      <c r="G25">
+        <v>46.5</v>
+      </c>
+      <c r="H25">
+        <v>288.1</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>38.3</v>
+      </c>
+      <c r="K25">
+        <v>18.5</v>
+      </c>
+      <c r="L25">
+        <v>19.8</v>
+      </c>
+      <c r="M25">
+        <v>3.389410640000001</v>
+      </c>
+      <c r="N25">
+        <v>16.41058936</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>16.41058936</v>
+      </c>
+      <c r="Q25">
+        <v>34.91058936</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1565579527715035</v>
+      </c>
+      <c r="T25">
+        <v>2.150182024875392</v>
+      </c>
+      <c r="U25">
+        <v>0.0509</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0.0509</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>5.841723562890566</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1323776236340577</v>
+      </c>
+      <c r="C26">
+        <v>212.656243759328</v>
+      </c>
+      <c r="D26">
+        <v>235.6410437593281</v>
+      </c>
+      <c r="E26">
+        <v>68.06480000000001</v>
+      </c>
+      <c r="F26">
+        <v>69.48480000000001</v>
+      </c>
+      <c r="G26">
+        <v>46.5</v>
+      </c>
+      <c r="H26">
+        <v>288.1</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>38.3</v>
+      </c>
+      <c r="K26">
+        <v>18.5</v>
+      </c>
+      <c r="L26">
+        <v>19.8</v>
+      </c>
+      <c r="M26">
+        <v>3.53677632</v>
+      </c>
+      <c r="N26">
+        <v>16.26322368</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>16.26322368</v>
+      </c>
+      <c r="Q26">
+        <v>34.76322368</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1581073995184969</v>
+      </c>
+      <c r="T26">
+        <v>2.178473893623752</v>
+      </c>
+      <c r="U26">
+        <v>0.0509</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0.0509</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>5.598318414436793</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1324986236340577</v>
+      </c>
+      <c r="C27">
+        <v>209.4567429575762</v>
+      </c>
+      <c r="D27">
+        <v>235.3367429575763</v>
+      </c>
+      <c r="E27">
+        <v>70.96000000000001</v>
+      </c>
+      <c r="F27">
+        <v>72.38000000000001</v>
+      </c>
+      <c r="G27">
+        <v>46.5</v>
+      </c>
+      <c r="H27">
+        <v>288.1</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>38.3</v>
+      </c>
+      <c r="K27">
+        <v>18.5</v>
+      </c>
+      <c r="L27">
+        <v>19.8</v>
+      </c>
+      <c r="M27">
+        <v>3.684142</v>
+      </c>
+      <c r="N27">
+        <v>16.115858</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>16.115858</v>
+      </c>
+      <c r="Q27">
+        <v>34.615858</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1596981648454102</v>
+      </c>
+      <c r="T27">
+        <v>2.207520212205402</v>
+      </c>
+      <c r="U27">
+        <v>0.0509</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0.0509</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>5.374385677859322</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1326196236340577</v>
+      </c>
+      <c r="C28">
+        <v>206.2580270747058</v>
+      </c>
+      <c r="D28">
+        <v>235.0332270747058</v>
+      </c>
+      <c r="E28">
+        <v>73.85520000000001</v>
+      </c>
+      <c r="F28">
+        <v>75.27520000000001</v>
+      </c>
+      <c r="G28">
+        <v>46.5</v>
+      </c>
+      <c r="H28">
+        <v>288.1</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>38.3</v>
+      </c>
+      <c r="K28">
+        <v>18.5</v>
+      </c>
+      <c r="L28">
+        <v>19.8</v>
+      </c>
+      <c r="M28">
+        <v>3.831507680000001</v>
+      </c>
+      <c r="N28">
+        <v>15.96849232</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>15.96849232</v>
+      </c>
+      <c r="Q28">
+        <v>34.46849232</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1613319238298077</v>
+      </c>
+      <c r="T28">
+        <v>2.237351566424394</v>
+      </c>
+      <c r="U28">
+        <v>0.0509</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0.0509</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>5.167678536403194</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1327406236340577</v>
+      </c>
+      <c r="C29">
+        <v>203.0600930776778</v>
+      </c>
+      <c r="D29">
+        <v>234.7304930776778</v>
+      </c>
+      <c r="E29">
+        <v>76.75040000000001</v>
+      </c>
+      <c r="F29">
+        <v>78.17040000000001</v>
+      </c>
+      <c r="G29">
+        <v>46.5</v>
+      </c>
+      <c r="H29">
+        <v>288.1</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>38.3</v>
+      </c>
+      <c r="K29">
+        <v>18.5</v>
+      </c>
+      <c r="L29">
+        <v>19.8</v>
+      </c>
+      <c r="M29">
+        <v>3.978873360000001</v>
+      </c>
+      <c r="N29">
+        <v>15.82112664</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>15.82112664</v>
+      </c>
+      <c r="Q29">
+        <v>34.32112664</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1630104433343256</v>
+      </c>
+      <c r="T29">
+        <v>2.268000218019249</v>
+      </c>
+      <c r="U29">
+        <v>0.0509</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0.0509</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>4.976283035054927</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1328616236340577</v>
+      </c>
+      <c r="C30">
+        <v>199.8629379490602</v>
+      </c>
+      <c r="D30">
+        <v>234.4285379490603</v>
+      </c>
+      <c r="E30">
+        <v>79.64560000000002</v>
+      </c>
+      <c r="F30">
+        <v>81.06560000000002</v>
+      </c>
+      <c r="G30">
+        <v>46.5</v>
+      </c>
+      <c r="H30">
+        <v>288.1</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>38.3</v>
+      </c>
+      <c r="K30">
+        <v>18.5</v>
+      </c>
+      <c r="L30">
+        <v>19.8</v>
+      </c>
+      <c r="M30">
+        <v>4.126239040000001</v>
+      </c>
+      <c r="N30">
+        <v>15.67376096</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>15.67376096</v>
+      </c>
+      <c r="Q30">
+        <v>34.17376096</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1647355883806357</v>
+      </c>
+      <c r="T30">
+        <v>2.299500221047293</v>
+      </c>
+      <c r="U30">
+        <v>0.0509</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0.0509</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>4.798558640945823</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1329826236340577</v>
+      </c>
+      <c r="C31">
+        <v>196.6665586869275</v>
+      </c>
+      <c r="D31">
+        <v>234.1273586869275</v>
+      </c>
+      <c r="E31">
+        <v>82.5408</v>
+      </c>
+      <c r="F31">
+        <v>83.96080000000001</v>
+      </c>
+      <c r="G31">
+        <v>46.5</v>
+      </c>
+      <c r="H31">
+        <v>288.1</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>38.3</v>
+      </c>
+      <c r="K31">
+        <v>18.5</v>
+      </c>
+      <c r="L31">
+        <v>19.8</v>
+      </c>
+      <c r="M31">
+        <v>4.273604720000001</v>
+      </c>
+      <c r="N31">
+        <v>15.52639528</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>15.52639528</v>
+      </c>
+      <c r="Q31">
+        <v>34.02639528</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.166509329062053</v>
+      </c>
+      <c r="T31">
+        <v>2.331887548104298</v>
+      </c>
+      <c r="U31">
+        <v>0.0509</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0.0509</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>4.633091101602863</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1338836236340577</v>
+      </c>
+      <c r="C32">
+        <v>191.5527984121446</v>
+      </c>
+      <c r="D32">
+        <v>231.9087984121446</v>
+      </c>
+      <c r="E32">
+        <v>85.43600000000001</v>
+      </c>
+      <c r="F32">
+        <v>86.85600000000001</v>
+      </c>
+      <c r="G32">
+        <v>46.5</v>
+      </c>
+      <c r="H32">
+        <v>288.1</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>38.3</v>
+      </c>
+      <c r="K32">
+        <v>18.5</v>
+      </c>
+      <c r="L32">
+        <v>19.8</v>
+      </c>
+      <c r="M32">
+        <v>4.646796</v>
+      </c>
+      <c r="N32">
+        <v>15.153204</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>15.153204</v>
+      </c>
+      <c r="Q32">
+        <v>33.653204</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1683337480486538</v>
+      </c>
+      <c r="T32">
+        <v>2.365200227362931</v>
+      </c>
+      <c r="U32">
+        <v>0.0535</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0.0535</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>4.261000482913389</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1340306236340577</v>
+      </c>
+      <c r="C33">
+        <v>188.2996190976587</v>
+      </c>
+      <c r="D33">
+        <v>231.5508190976588</v>
+      </c>
+      <c r="E33">
+        <v>88.33120000000001</v>
+      </c>
+      <c r="F33">
+        <v>89.75120000000001</v>
+      </c>
+      <c r="G33">
+        <v>46.5</v>
+      </c>
+      <c r="H33">
+        <v>288.1</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>38.3</v>
+      </c>
+      <c r="K33">
+        <v>18.5</v>
+      </c>
+      <c r="L33">
+        <v>19.8</v>
+      </c>
+      <c r="M33">
+        <v>4.8016892</v>
+      </c>
+      <c r="N33">
+        <v>14.9983108</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>14.9983108</v>
+      </c>
+      <c r="Q33">
+        <v>33.4983108</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1702110487450111</v>
+      </c>
+      <c r="T33">
+        <v>2.399478491527611</v>
+      </c>
+      <c r="U33">
+        <v>0.0535</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0.0535</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>4.123548854432311</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1350416236340577</v>
+      </c>
+      <c r="C34">
+        <v>182.9720216663991</v>
+      </c>
+      <c r="D34">
+        <v>229.1184216663992</v>
+      </c>
+      <c r="E34">
+        <v>91.22640000000001</v>
+      </c>
+      <c r="F34">
+        <v>92.64640000000001</v>
+      </c>
+      <c r="G34">
+        <v>46.5</v>
+      </c>
+      <c r="H34">
+        <v>288.1</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>38.3</v>
+      </c>
+      <c r="K34">
+        <v>18.5</v>
+      </c>
+      <c r="L34">
+        <v>19.8</v>
+      </c>
+      <c r="M34">
+        <v>5.206727680000001</v>
+      </c>
+      <c r="N34">
+        <v>14.59327232</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>14.59327232</v>
+      </c>
+      <c r="Q34">
+        <v>33.09327232</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1721435641677319</v>
+      </c>
+      <c r="T34">
+        <v>2.434764939932429</v>
+      </c>
+      <c r="U34">
+        <v>0.0562</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0.0562</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>3.802772339343854</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1352156236340577</v>
+      </c>
+      <c r="C35">
+        <v>179.66333468299</v>
+      </c>
+      <c r="D35">
+        <v>228.7049346829901</v>
+      </c>
+      <c r="E35">
+        <v>94.12160000000002</v>
+      </c>
+      <c r="F35">
+        <v>95.54160000000002</v>
+      </c>
+      <c r="G35">
+        <v>46.5</v>
+      </c>
+      <c r="H35">
+        <v>288.1</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>38.3</v>
+      </c>
+      <c r="K35">
+        <v>18.5</v>
+      </c>
+      <c r="L35">
+        <v>19.8</v>
+      </c>
+      <c r="M35">
+        <v>5.369437920000001</v>
+      </c>
+      <c r="N35">
+        <v>14.43056208</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>14.43056208</v>
+      </c>
+      <c r="Q35">
+        <v>32.93056207999999</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1741337666179965</v>
+      </c>
+      <c r="T35">
+        <v>2.471104715155301</v>
+      </c>
+      <c r="U35">
+        <v>0.0562</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0.0562</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>3.687536813909192</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1353896236340577</v>
+      </c>
+      <c r="C36">
+        <v>176.3561374400398</v>
+      </c>
+      <c r="D36">
+        <v>228.2929374400398</v>
+      </c>
+      <c r="E36">
+        <v>97.01680000000002</v>
+      </c>
+      <c r="F36">
+        <v>98.43680000000002</v>
+      </c>
+      <c r="G36">
+        <v>46.5</v>
+      </c>
+      <c r="H36">
+        <v>288.1</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>38.3</v>
+      </c>
+      <c r="K36">
+        <v>18.5</v>
+      </c>
+      <c r="L36">
+        <v>19.8</v>
+      </c>
+      <c r="M36">
+        <v>5.532148160000001</v>
+      </c>
+      <c r="N36">
+        <v>14.26785184</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>14.26785184</v>
+      </c>
+      <c r="Q36">
+        <v>32.76785183999999</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1761842782334207</v>
+      </c>
+      <c r="T36">
+        <v>2.508545695687957</v>
+      </c>
+      <c r="U36">
+        <v>0.0562</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0.0562</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>3.579079848794215</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1372086236340577</v>
+      </c>
+      <c r="C37">
+        <v>169.2411359849596</v>
+      </c>
+      <c r="D37">
+        <v>224.0731359849596</v>
+      </c>
+      <c r="E37">
+        <v>99.91200000000002</v>
+      </c>
+      <c r="F37">
+        <v>101.332</v>
+      </c>
+      <c r="G37">
+        <v>46.5</v>
+      </c>
+      <c r="H37">
+        <v>288.1</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>38.3</v>
+      </c>
+      <c r="K37">
+        <v>18.5</v>
+      </c>
+      <c r="L37">
+        <v>19.8</v>
+      </c>
+      <c r="M37">
+        <v>6.171118800000001</v>
+      </c>
+      <c r="N37">
+        <v>13.6288812</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>13.6288812</v>
+      </c>
+      <c r="Q37">
+        <v>32.1288812</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1782978825139349</v>
+      </c>
+      <c r="T37">
+        <v>2.547138706390848</v>
+      </c>
+      <c r="U37">
+        <v>0.0609</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0.0609</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>3.208494381926337</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1374296236340577</v>
+      </c>
+      <c r="C38">
+        <v>165.8438539407615</v>
+      </c>
+      <c r="D38">
+        <v>223.5710539407615</v>
+      </c>
+      <c r="E38">
+        <v>102.8072</v>
+      </c>
+      <c r="F38">
+        <v>104.2272</v>
+      </c>
+      <c r="G38">
+        <v>46.5</v>
+      </c>
+      <c r="H38">
+        <v>288.1</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>38.3</v>
+      </c>
+      <c r="K38">
+        <v>18.5</v>
+      </c>
+      <c r="L38">
+        <v>19.8</v>
+      </c>
+      <c r="M38">
+        <v>6.347436480000001</v>
+      </c>
+      <c r="N38">
+        <v>13.45256352</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>13.45256352</v>
+      </c>
+      <c r="Q38">
+        <v>31.95256352</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1804775369282151</v>
+      </c>
+      <c r="T38">
+        <v>2.586937748678205</v>
+      </c>
+      <c r="U38">
+        <v>0.0609</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0.0609</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>3.119369537983939</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1376506236340577</v>
+      </c>
+      <c r="C39">
+        <v>162.4488169027695</v>
+      </c>
+      <c r="D39">
+        <v>223.0712169027695</v>
+      </c>
+      <c r="E39">
+        <v>105.7024</v>
+      </c>
+      <c r="F39">
+        <v>107.1224</v>
+      </c>
+      <c r="G39">
+        <v>46.5</v>
+      </c>
+      <c r="H39">
+        <v>288.1</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>38.3</v>
+      </c>
+      <c r="K39">
+        <v>18.5</v>
+      </c>
+      <c r="L39">
+        <v>19.8</v>
+      </c>
+      <c r="M39">
+        <v>6.523754160000001</v>
+      </c>
+      <c r="N39">
+        <v>13.27624584</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>13.27624584</v>
+      </c>
+      <c r="Q39">
+        <v>31.77624583999999</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1827263867207265</v>
+      </c>
+      <c r="T39">
+        <v>2.628000252625479</v>
+      </c>
+      <c r="U39">
+        <v>0.0609</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0.0609</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>3.035062253173562</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1414056236340577</v>
+      </c>
+      <c r="C40">
+        <v>151.390005691192</v>
+      </c>
+      <c r="D40">
+        <v>214.9076056911919</v>
+      </c>
+      <c r="E40">
+        <v>108.5976</v>
+      </c>
+      <c r="F40">
+        <v>110.0176</v>
+      </c>
+      <c r="G40">
+        <v>46.5</v>
+      </c>
+      <c r="H40">
+        <v>288.1</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>38.3</v>
+      </c>
+      <c r="K40">
+        <v>18.5</v>
+      </c>
+      <c r="L40">
+        <v>19.8</v>
+      </c>
+      <c r="M40">
+        <v>7.723235520000001</v>
+      </c>
+      <c r="N40">
+        <v>12.07676448</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>12.07676448</v>
+      </c>
+      <c r="Q40">
+        <v>30.57676447999999</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1850477800549317</v>
+      </c>
+      <c r="T40">
+        <v>2.670387353474276</v>
+      </c>
+      <c r="U40">
+        <v>0.0702</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0.0702</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>2.563692373322832</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1435526236340577</v>
+      </c>
+      <c r="C41">
+        <v>144.0900794570228</v>
+      </c>
+      <c r="D41">
+        <v>210.5028794570228</v>
+      </c>
+      <c r="E41">
+        <v>111.4928</v>
+      </c>
+      <c r="F41">
+        <v>112.9128</v>
+      </c>
+      <c r="G41">
+        <v>46.5</v>
+      </c>
+      <c r="H41">
+        <v>288.1</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>38.3</v>
+      </c>
+      <c r="K41">
+        <v>18.5</v>
+      </c>
+      <c r="L41">
+        <v>19.8</v>
+      </c>
+      <c r="M41">
+        <v>8.45716872</v>
+      </c>
+      <c r="N41">
+        <v>11.34283128</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>11.34283128</v>
+      </c>
+      <c r="Q41">
+        <v>29.84283128</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1874452846459962</v>
+      </c>
+      <c r="T41">
+        <v>2.714164195334511</v>
+      </c>
+      <c r="U41">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>2.341209056545818</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1439136236340577</v>
+      </c>
+      <c r="C42">
+        <v>140.4719328316781</v>
+      </c>
+      <c r="D42">
+        <v>209.7799328316781</v>
+      </c>
+      <c r="E42">
+        <v>114.388</v>
+      </c>
+      <c r="F42">
+        <v>115.808</v>
+      </c>
+      <c r="G42">
+        <v>46.5</v>
+      </c>
+      <c r="H42">
+        <v>288.1</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>38.3</v>
+      </c>
+      <c r="K42">
+        <v>18.5</v>
+      </c>
+      <c r="L42">
+        <v>19.8</v>
+      </c>
+      <c r="M42">
+        <v>8.674019200000002</v>
+      </c>
+      <c r="N42">
+        <v>11.1259808</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>11.1259808</v>
+      </c>
+      <c r="Q42">
+        <v>29.62598079999999</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1899227060567628</v>
+      </c>
+      <c r="T42">
+        <v>2.759400265256752</v>
+      </c>
+      <c r="U42">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>2.282678830132172</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1442746236340577</v>
+      </c>
+      <c r="C43">
+        <v>136.8587349555731</v>
+      </c>
+      <c r="D43">
+        <v>209.0619349555731</v>
+      </c>
+      <c r="E43">
+        <v>117.2832</v>
+      </c>
+      <c r="F43">
+        <v>118.7032</v>
+      </c>
+      <c r="G43">
+        <v>46.5</v>
+      </c>
+      <c r="H43">
+        <v>288.1</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>38.3</v>
+      </c>
+      <c r="K43">
+        <v>18.5</v>
+      </c>
+      <c r="L43">
+        <v>19.8</v>
+      </c>
+      <c r="M43">
+        <v>8.890869680000002</v>
+      </c>
+      <c r="N43">
+        <v>10.90913032</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>10.90913032</v>
+      </c>
+      <c r="Q43">
+        <v>29.40913032</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.192484107854335</v>
+      </c>
+      <c r="T43">
+        <v>2.806169761278053</v>
+      </c>
+      <c r="U43">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>2.227003736714314</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1446356236340577</v>
+      </c>
+      <c r="C44">
+        <v>133.2504351889017</v>
+      </c>
+      <c r="D44">
+        <v>208.3488351889017</v>
+      </c>
+      <c r="E44">
+        <v>120.1784</v>
+      </c>
+      <c r="F44">
+        <v>121.5984</v>
+      </c>
+      <c r="G44">
+        <v>46.5</v>
+      </c>
+      <c r="H44">
+        <v>288.1</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>38.3</v>
+      </c>
+      <c r="K44">
+        <v>18.5</v>
+      </c>
+      <c r="L44">
+        <v>19.8</v>
+      </c>
+      <c r="M44">
+        <v>9.10772016</v>
+      </c>
+      <c r="N44">
+        <v>10.69227984</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>10.69227984</v>
+      </c>
+      <c r="Q44">
+        <v>29.19227984</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1951338338518236</v>
+      </c>
+      <c r="T44">
+        <v>2.854551998541468</v>
+      </c>
+      <c r="U44">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>2.173979838221117</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1449966236340577</v>
+      </c>
+      <c r="C45">
+        <v>129.646983580429</v>
+      </c>
+      <c r="D45">
+        <v>207.640583580429</v>
+      </c>
+      <c r="E45">
+        <v>123.0736</v>
+      </c>
+      <c r="F45">
+        <v>124.4936</v>
+      </c>
+      <c r="G45">
+        <v>46.5</v>
+      </c>
+      <c r="H45">
+        <v>288.1</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>38.3</v>
+      </c>
+      <c r="K45">
+        <v>18.5</v>
+      </c>
+      <c r="L45">
+        <v>19.8</v>
+      </c>
+      <c r="M45">
+        <v>9.324570640000001</v>
+      </c>
+      <c r="N45">
+        <v>10.47542936</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>10.47542936</v>
+      </c>
+      <c r="Q45">
+        <v>28.97542936</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1978765326913292</v>
+      </c>
+      <c r="T45">
+        <v>2.904631858165002</v>
+      </c>
+      <c r="U45">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>2.123422167564812</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1453576236340577</v>
+      </c>
+      <c r="C46">
+        <v>126.0483308558265</v>
+      </c>
+      <c r="D46">
+        <v>206.9371308558266</v>
+      </c>
+      <c r="E46">
+        <v>125.9688</v>
+      </c>
+      <c r="F46">
+        <v>127.3888</v>
+      </c>
+      <c r="G46">
+        <v>46.5</v>
+      </c>
+      <c r="H46">
+        <v>288.1</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>38.3</v>
+      </c>
+      <c r="K46">
+        <v>18.5</v>
+      </c>
+      <c r="L46">
+        <v>19.8</v>
+      </c>
+      <c r="M46">
+        <v>9.541421120000001</v>
+      </c>
+      <c r="N46">
+        <v>10.25857888</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>10.25857888</v>
+      </c>
+      <c r="Q46">
+        <v>28.75857887999999</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2007171850608173</v>
+      </c>
+      <c r="T46">
+        <v>2.956500284203663</v>
+      </c>
+      <c r="U46">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>2.075162572847429</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1457186236340577</v>
+      </c>
+      <c r="C47">
+        <v>122.4544284062455</v>
+      </c>
+      <c r="D47">
+        <v>206.2384284062455</v>
+      </c>
+      <c r="E47">
+        <v>128.864</v>
+      </c>
+      <c r="F47">
+        <v>130.284</v>
+      </c>
+      <c r="G47">
+        <v>46.5</v>
+      </c>
+      <c r="H47">
+        <v>288.1</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>38.3</v>
+      </c>
+      <c r="K47">
+        <v>18.5</v>
+      </c>
+      <c r="L47">
+        <v>19.8</v>
+      </c>
+      <c r="M47">
+        <v>9.7582716</v>
+      </c>
+      <c r="N47">
+        <v>10.0417284</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>10.0417284</v>
+      </c>
+      <c r="Q47">
+        <v>28.5417284</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2036611338801049</v>
+      </c>
+      <c r="T47">
+        <v>3.010254834825548</v>
+      </c>
+      <c r="U47">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>2.029047849006375</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1535776236340577</v>
+      </c>
+      <c r="C48">
+        <v>105.4377667700268</v>
+      </c>
+      <c r="D48">
+        <v>192.1169667700269</v>
+      </c>
+      <c r="E48">
+        <v>131.7592</v>
+      </c>
+      <c r="F48">
+        <v>133.1792</v>
+      </c>
+      <c r="G48">
+        <v>46.5</v>
+      </c>
+      <c r="H48">
+        <v>288.1</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>38.3</v>
+      </c>
+      <c r="K48">
+        <v>18.5</v>
+      </c>
+      <c r="L48">
+        <v>19.8</v>
+      </c>
+      <c r="M48">
+        <v>12.14594304</v>
+      </c>
+      <c r="N48">
+        <v>7.654056959999997</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>7.654056959999997</v>
+      </c>
+      <c r="Q48">
+        <v>26.15405695999999</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2067141178408475</v>
+      </c>
+      <c r="T48">
+        <v>3.066000294729725</v>
+      </c>
+      <c r="U48">
+        <v>0.0912</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0.0912</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>1.630173954775931</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1541016236340577</v>
+      </c>
+      <c r="C49">
+        <v>101.669471600899</v>
+      </c>
+      <c r="D49">
+        <v>191.243871600899</v>
+      </c>
+      <c r="E49">
+        <v>134.6544</v>
+      </c>
+      <c r="F49">
+        <v>136.0744</v>
+      </c>
+      <c r="G49">
+        <v>46.5</v>
+      </c>
+      <c r="H49">
+        <v>288.1</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>38.3</v>
+      </c>
+      <c r="K49">
+        <v>18.5</v>
+      </c>
+      <c r="L49">
+        <v>19.8</v>
+      </c>
+      <c r="M49">
+        <v>12.40998528</v>
+      </c>
+      <c r="N49">
+        <v>7.390014719999998</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>7.390014719999998</v>
+      </c>
+      <c r="Q49">
+        <v>25.89001472</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2098823087435051</v>
+      </c>
+      <c r="T49">
+        <v>3.123849356894437</v>
+      </c>
+      <c r="U49">
+        <v>0.0912</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0.0912</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>1.595489402546656</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1546256236340577</v>
+      </c>
+      <c r="C50">
+        <v>97.90907627041256</v>
+      </c>
+      <c r="D50">
+        <v>190.3786762704126</v>
+      </c>
+      <c r="E50">
+        <v>137.5496</v>
+      </c>
+      <c r="F50">
+        <v>138.9696</v>
+      </c>
+      <c r="G50">
+        <v>46.5</v>
+      </c>
+      <c r="H50">
+        <v>288.1</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>38.3</v>
+      </c>
+      <c r="K50">
+        <v>18.5</v>
+      </c>
+      <c r="L50">
+        <v>19.8</v>
+      </c>
+      <c r="M50">
+        <v>12.67402752</v>
+      </c>
+      <c r="N50">
+        <v>7.12597248</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>7.12597248</v>
+      </c>
+      <c r="Q50">
+        <v>25.62597247999999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2131723531424186</v>
+      </c>
+      <c r="T50">
+        <v>3.18392338298856</v>
+      </c>
+      <c r="U50">
+        <v>0.0912</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0.0912</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>1.562250039993601</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1551496236340577</v>
+      </c>
+      <c r="C51">
+        <v>94.15647404383162</v>
+      </c>
+      <c r="D51">
+        <v>189.5212740438316</v>
+      </c>
+      <c r="E51">
+        <v>140.4448</v>
+      </c>
+      <c r="F51">
+        <v>141.8648</v>
+      </c>
+      <c r="G51">
+        <v>46.5</v>
+      </c>
+      <c r="H51">
+        <v>288.1</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>38.3</v>
+      </c>
+      <c r="K51">
+        <v>18.5</v>
+      </c>
+      <c r="L51">
+        <v>19.8</v>
+      </c>
+      <c r="M51">
+        <v>12.93806976</v>
+      </c>
+      <c r="N51">
+        <v>6.86193024</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>6.86193024</v>
+      </c>
+      <c r="Q51">
+        <v>25.36193024</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2165914188903092</v>
+      </c>
+      <c r="T51">
+        <v>3.246353253243238</v>
+      </c>
+      <c r="U51">
+        <v>0.0912</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0.0912</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>1.53036738611618</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1883736236340577</v>
+      </c>
+      <c r="C52">
+        <v>49.16391318669633</v>
+      </c>
+      <c r="D52">
+        <v>147.4239131866964</v>
+      </c>
+      <c r="E52">
+        <v>143.34</v>
+      </c>
+      <c r="F52">
+        <v>144.76</v>
+      </c>
+      <c r="G52">
+        <v>46.5</v>
+      </c>
+      <c r="H52">
+        <v>288.1</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>38.3</v>
+      </c>
+      <c r="K52">
+        <v>18.5</v>
+      </c>
+      <c r="L52">
+        <v>19.8</v>
+      </c>
+      <c r="M52">
+        <v>22.66941600000001</v>
+      </c>
+      <c r="N52">
+        <v>-2.869416000000005</v>
+      </c>
+      <c r="O52">
         <v>-0</v>
       </c>
-      <c r="N4">
+      <c r="P52">
+        <v>-2.869416000000005</v>
+      </c>
+      <c r="Q52">
+        <v>15.63058399999999</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2201472472681154</v>
+      </c>
+      <c r="T52">
+        <v>3.311280318308103</v>
+      </c>
+      <c r="U52">
+        <v>0.1566</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0.1566</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.8734234706355027</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1895516236340577</v>
+      </c>
+      <c r="C53">
+        <v>45.11671650800386</v>
+      </c>
+      <c r="D53">
+        <v>146.2719165080039</v>
+      </c>
+      <c r="E53">
+        <v>146.2352</v>
+      </c>
+      <c r="F53">
+        <v>147.6552</v>
+      </c>
+      <c r="G53">
+        <v>46.5</v>
+      </c>
+      <c r="H53">
+        <v>288.1</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>38.3</v>
+      </c>
+      <c r="K53">
+        <v>18.5</v>
+      </c>
+      <c r="L53">
+        <v>19.8</v>
+      </c>
+      <c r="M53">
+        <v>23.12280432000001</v>
+      </c>
+      <c r="N53">
+        <v>-3.322804320000007</v>
+      </c>
+      <c r="O53">
         <v>-0</v>
       </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
+      <c r="P53">
+        <v>-3.322804320000007</v>
+      </c>
+      <c r="Q53">
+        <v>15.17719567999999</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2238482114980769</v>
+      </c>
+      <c r="T53">
+        <v>3.37885746766133</v>
+      </c>
+      <c r="U53">
+        <v>0.1566</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0.1566</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.856297520230885</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1907296236340577</v>
+      </c>
+      <c r="C54">
+        <v>41.08738404900788</v>
+      </c>
+      <c r="D54">
+        <v>145.1377840490079</v>
+      </c>
+      <c r="E54">
+        <v>149.1304</v>
+      </c>
+      <c r="F54">
+        <v>150.5504</v>
+      </c>
+      <c r="G54">
+        <v>46.5</v>
+      </c>
+      <c r="H54">
+        <v>288.1</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>38.3</v>
+      </c>
+      <c r="K54">
+        <v>18.5</v>
+      </c>
+      <c r="L54">
+        <v>19.8</v>
+      </c>
+      <c r="M54">
+        <v>23.57619264000001</v>
+      </c>
+      <c r="N54">
+        <v>-3.776192640000005</v>
+      </c>
+      <c r="O54">
         <v>-0</v>
       </c>
-      <c r="Q4">
+      <c r="P54">
+        <v>-3.776192640000005</v>
+      </c>
+      <c r="Q54">
+        <v>14.72380735999999</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2277033825709535</v>
+      </c>
+      <c r="T54">
+        <v>3.449250331570941</v>
+      </c>
+      <c r="U54">
+        <v>0.1566</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0.1566</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.8398302602264449</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1919076236340577</v>
+      </c>
+      <c r="C55">
+        <v>37.07550347130933</v>
+      </c>
+      <c r="D55">
+        <v>144.0211034713094</v>
+      </c>
+      <c r="E55">
+        <v>152.0256000000001</v>
+      </c>
+      <c r="F55">
+        <v>153.4456</v>
+      </c>
+      <c r="G55">
+        <v>46.5</v>
+      </c>
+      <c r="H55">
+        <v>288.1</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>38.3</v>
+      </c>
+      <c r="K55">
+        <v>18.5</v>
+      </c>
+      <c r="L55">
+        <v>19.8</v>
+      </c>
+      <c r="M55">
+        <v>24.02958096000001</v>
+      </c>
+      <c r="N55">
+        <v>-4.229580960000007</v>
+      </c>
+      <c r="O55">
         <v>-0</v>
       </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>8.27</v>
-      </c>
-      <c r="V4">
-        <v>0.2356125356125356</v>
-      </c>
-      <c r="W4">
-        <v>-0.1400468384074942</v>
-      </c>
-      <c r="X4">
-        <v>0.2519055044010787</v>
-      </c>
-      <c r="Y4">
-        <v>-0.3919523428085729</v>
-      </c>
-      <c r="Z4">
-        <v>0.6518058690744922</v>
-      </c>
-      <c r="AA4">
-        <v>-0.08338036117381491</v>
-      </c>
-      <c r="AB4">
-        <v>0.1658171243294886</v>
-      </c>
-      <c r="AC4">
-        <v>-0.2491974855033036</v>
-      </c>
-      <c r="AD4">
-        <v>29.2</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>29.2</v>
-      </c>
-      <c r="AG4">
-        <v>20.93</v>
-      </c>
-      <c r="AH4">
-        <v>0.4541213063763608</v>
-      </c>
-      <c r="AI4">
-        <v>0.4657097288676236</v>
-      </c>
-      <c r="AJ4">
-        <v>0.3735498839907193</v>
-      </c>
-      <c r="AK4">
-        <v>0.3845305897483006</v>
-      </c>
-      <c r="AL4">
-        <v>1.15</v>
-      </c>
-      <c r="AM4">
-        <v>1.135</v>
-      </c>
-      <c r="AN4">
-        <v>-10.46594982078853</v>
-      </c>
-      <c r="AO4">
-        <v>-5.139130434782609</v>
-      </c>
-      <c r="AP4">
-        <v>-7.50179211469534</v>
-      </c>
-      <c r="AQ4">
-        <v>-5.20704845814978</v>
+      <c r="P55">
+        <v>-4.229580960000007</v>
+      </c>
+      <c r="Q55">
+        <v>14.27041903999999</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2317226034767185</v>
+      </c>
+      <c r="T55">
+        <v>3.522638636497982</v>
+      </c>
+      <c r="U55">
+        <v>0.1566</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0.1566</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.8239844062599082</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1930856236340577</v>
+      </c>
+      <c r="C56">
+        <v>33.08067502963675</v>
+      </c>
+      <c r="D56">
+        <v>142.9214750296368</v>
+      </c>
+      <c r="E56">
+        <v>154.9208</v>
+      </c>
+      <c r="F56">
+        <v>156.3408</v>
+      </c>
+      <c r="G56">
+        <v>46.5</v>
+      </c>
+      <c r="H56">
+        <v>288.1</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>38.3</v>
+      </c>
+      <c r="K56">
+        <v>18.5</v>
+      </c>
+      <c r="L56">
+        <v>19.8</v>
+      </c>
+      <c r="M56">
+        <v>24.48296928000001</v>
+      </c>
+      <c r="N56">
+        <v>-4.682969280000005</v>
+      </c>
+      <c r="O56">
+        <v>-0</v>
+      </c>
+      <c r="P56">
+        <v>-4.682969280000005</v>
+      </c>
+      <c r="Q56">
+        <v>13.81703071999999</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2359165731175167</v>
+      </c>
+      <c r="T56">
+        <v>3.599217737291416</v>
+      </c>
+      <c r="U56">
+        <v>0.1566</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0.1566</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.8087254357736137</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2229736236340577</v>
+      </c>
+      <c r="C57">
+        <v>6.991941876522048</v>
+      </c>
+      <c r="D57">
+        <v>119.7279418765221</v>
+      </c>
+      <c r="E57">
+        <v>157.8160000000001</v>
+      </c>
+      <c r="F57">
+        <v>159.236</v>
+      </c>
+      <c r="G57">
+        <v>46.5</v>
+      </c>
+      <c r="H57">
+        <v>288.1</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>38.3</v>
+      </c>
+      <c r="K57">
+        <v>18.5</v>
+      </c>
+      <c r="L57">
+        <v>19.8</v>
+      </c>
+      <c r="M57">
+        <v>33.24847680000001</v>
+      </c>
+      <c r="N57">
+        <v>-13.44847680000001</v>
+      </c>
+      <c r="O57">
+        <v>-0</v>
+      </c>
+      <c r="P57">
+        <v>-13.44847680000001</v>
+      </c>
+      <c r="Q57">
+        <v>5.051523199999984</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2402969414090171</v>
+      </c>
+      <c r="T57">
+        <v>3.67920035367567</v>
+      </c>
+      <c r="U57">
+        <v>0.2088</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0.2088</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.5955160027060244</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2246736236340577</v>
+      </c>
+      <c r="C58">
+        <v>3.001710224313001</v>
+      </c>
+      <c r="D58">
+        <v>118.632910224313</v>
+      </c>
+      <c r="E58">
+        <v>160.7112</v>
+      </c>
+      <c r="F58">
+        <v>162.1312</v>
+      </c>
+      <c r="G58">
+        <v>46.5</v>
+      </c>
+      <c r="H58">
+        <v>288.1</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>38.3</v>
+      </c>
+      <c r="K58">
+        <v>18.5</v>
+      </c>
+      <c r="L58">
+        <v>19.8</v>
+      </c>
+      <c r="M58">
+        <v>33.85299456000001</v>
+      </c>
+      <c r="N58">
+        <v>-14.05299456000001</v>
+      </c>
+      <c r="O58">
+        <v>-0</v>
+      </c>
+      <c r="P58">
+        <v>-14.05299456000001</v>
+      </c>
+      <c r="Q58">
+        <v>4.447005439999991</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2448764173501311</v>
+      </c>
+      <c r="T58">
+        <v>3.762818543531936</v>
+      </c>
+      <c r="U58">
+        <v>0.2088</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0.2088</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.5848817883719885</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2263736236340577</v>
+      </c>
+      <c r="C59">
+        <v>-0.968672647745791</v>
+      </c>
+      <c r="D59">
+        <v>117.5577273522543</v>
+      </c>
+      <c r="E59">
+        <v>163.6064000000001</v>
+      </c>
+      <c r="F59">
+        <v>165.0264000000001</v>
+      </c>
+      <c r="G59">
+        <v>46.5</v>
+      </c>
+      <c r="H59">
+        <v>288.1</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>38.3</v>
+      </c>
+      <c r="K59">
+        <v>18.5</v>
+      </c>
+      <c r="L59">
+        <v>19.8</v>
+      </c>
+      <c r="M59">
+        <v>34.45751232000001</v>
+      </c>
+      <c r="N59">
+        <v>-14.65751232000001</v>
+      </c>
+      <c r="O59">
+        <v>-0</v>
+      </c>
+      <c r="P59">
+        <v>-14.65751232000001</v>
+      </c>
+      <c r="Q59">
+        <v>3.842487679999984</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2496688921722272</v>
+      </c>
+      <c r="T59">
+        <v>3.850325951521051</v>
+      </c>
+      <c r="U59">
+        <v>0.2088</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0.2088</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.5746207043654623</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2280736236340577</v>
+      </c>
+      <c r="C60">
+        <v>-4.919741567364554</v>
+      </c>
+      <c r="D60">
+        <v>116.5018584326355</v>
+      </c>
+      <c r="E60">
+        <v>166.5016</v>
+      </c>
+      <c r="F60">
+        <v>167.9216</v>
+      </c>
+      <c r="G60">
+        <v>46.5</v>
+      </c>
+      <c r="H60">
+        <v>288.1</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>38.3</v>
+      </c>
+      <c r="K60">
+        <v>18.5</v>
+      </c>
+      <c r="L60">
+        <v>19.8</v>
+      </c>
+      <c r="M60">
+        <v>35.06203008000001</v>
+      </c>
+      <c r="N60">
+        <v>-15.26203008000001</v>
+      </c>
+      <c r="O60">
+        <v>-0</v>
+      </c>
+      <c r="P60">
+        <v>-15.26203008000001</v>
+      </c>
+      <c r="Q60">
+        <v>3.237969919999991</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2546895800810897</v>
+      </c>
+      <c r="T60">
+        <v>3.942000378938217</v>
+      </c>
+      <c r="U60">
+        <v>0.2088</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>0.2088</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.5647134508419199</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2297736236340577</v>
+      </c>
+      <c r="C61">
+        <v>-8.852012318637435</v>
+      </c>
+      <c r="D61">
+        <v>115.4647876813626</v>
+      </c>
+      <c r="E61">
+        <v>169.3968</v>
+      </c>
+      <c r="F61">
+        <v>170.8168</v>
+      </c>
+      <c r="G61">
+        <v>46.5</v>
+      </c>
+      <c r="H61">
+        <v>288.1</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>38.3</v>
+      </c>
+      <c r="K61">
+        <v>18.5</v>
+      </c>
+      <c r="L61">
+        <v>19.8</v>
+      </c>
+      <c r="M61">
+        <v>35.66654784</v>
+      </c>
+      <c r="N61">
+        <v>-15.86654784</v>
+      </c>
+      <c r="O61">
+        <v>-0</v>
+      </c>
+      <c r="P61">
+        <v>-15.86654784</v>
+      </c>
+      <c r="Q61">
+        <v>2.633452159999997</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2599551795952626</v>
+      </c>
+      <c r="T61">
+        <v>4.038146729644027</v>
+      </c>
+      <c r="U61">
+        <v>0.2088</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <v>0.2088</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.5551420364208706</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2314736236340577</v>
+      </c>
+      <c r="C62">
+        <v>-12.76598248217124</v>
+      </c>
+      <c r="D62">
+        <v>114.4460175178288</v>
+      </c>
+      <c r="E62">
+        <v>172.292</v>
+      </c>
+      <c r="F62">
+        <v>173.712</v>
+      </c>
+      <c r="G62">
+        <v>46.5</v>
+      </c>
+      <c r="H62">
+        <v>288.1</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>38.3</v>
+      </c>
+      <c r="K62">
+        <v>18.5</v>
+      </c>
+      <c r="L62">
+        <v>19.8</v>
+      </c>
+      <c r="M62">
+        <v>36.27106560000001</v>
+      </c>
+      <c r="N62">
+        <v>-16.47106560000001</v>
+      </c>
+      <c r="O62">
+        <v>-0</v>
+      </c>
+      <c r="P62">
+        <v>-16.47106560000001</v>
+      </c>
+      <c r="Q62">
+        <v>2.02893439999999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2654840590851442</v>
+      </c>
+      <c r="T62">
+        <v>4.139100397885128</v>
+      </c>
+      <c r="U62">
+        <v>0.2088</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>0.2088</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.5458896691471893</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2331736236340577</v>
+      </c>
+      <c r="C63">
+        <v>-16.66213223112791</v>
+      </c>
+      <c r="D63">
+        <v>113.4450677688721</v>
+      </c>
+      <c r="E63">
+        <v>175.1872</v>
+      </c>
+      <c r="F63">
+        <v>176.6072</v>
+      </c>
+      <c r="G63">
+        <v>46.5</v>
+      </c>
+      <c r="H63">
+        <v>288.1</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>38.3</v>
+      </c>
+      <c r="K63">
+        <v>18.5</v>
+      </c>
+      <c r="L63">
+        <v>19.8</v>
+      </c>
+      <c r="M63">
+        <v>36.87558336</v>
+      </c>
+      <c r="N63">
+        <v>-17.07558336</v>
+      </c>
+      <c r="O63">
+        <v>-0</v>
+      </c>
+      <c r="P63">
+        <v>-17.07558336</v>
+      </c>
+      <c r="Q63">
+        <v>1.424416639999997</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2712964708565582</v>
+      </c>
+      <c r="T63">
+        <v>4.245231177318081</v>
+      </c>
+      <c r="U63">
+        <v>0.2088</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0.2088</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.5369406581775633</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2348736236340577</v>
+      </c>
+      <c r="C64">
+        <v>-20.54092508585592</v>
+      </c>
+      <c r="D64">
+        <v>112.4614749141441</v>
+      </c>
+      <c r="E64">
+        <v>178.0824</v>
+      </c>
+      <c r="F64">
+        <v>179.5024</v>
+      </c>
+      <c r="G64">
+        <v>46.5</v>
+      </c>
+      <c r="H64">
+        <v>288.1</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>38.3</v>
+      </c>
+      <c r="K64">
+        <v>18.5</v>
+      </c>
+      <c r="L64">
+        <v>19.8</v>
+      </c>
+      <c r="M64">
+        <v>37.48010112000001</v>
+      </c>
+      <c r="N64">
+        <v>-17.68010112000001</v>
+      </c>
+      <c r="O64">
+        <v>-0</v>
+      </c>
+      <c r="P64">
+        <v>-17.68010112000001</v>
+      </c>
+      <c r="Q64">
+        <v>0.8198988799999896</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.277414799036994</v>
+      </c>
+      <c r="T64">
+        <v>4.356947787247504</v>
+      </c>
+      <c r="U64">
+        <v>0.2088</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0.2088</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.5282803249811509</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2365736236340577</v>
+      </c>
+      <c r="C65">
+        <v>-24.40280862960188</v>
+      </c>
+      <c r="D65">
+        <v>111.4947913703982</v>
+      </c>
+      <c r="E65">
+        <v>180.9776000000001</v>
+      </c>
+      <c r="F65">
+        <v>182.3976</v>
+      </c>
+      <c r="G65">
+        <v>46.5</v>
+      </c>
+      <c r="H65">
+        <v>288.1</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>38.3</v>
+      </c>
+      <c r="K65">
+        <v>18.5</v>
+      </c>
+      <c r="L65">
+        <v>19.8</v>
+      </c>
+      <c r="M65">
+        <v>38.08461888000001</v>
+      </c>
+      <c r="N65">
+        <v>-18.28461888000001</v>
+      </c>
+      <c r="O65">
+        <v>-0</v>
+      </c>
+      <c r="P65">
+        <v>-18.28461888000001</v>
+      </c>
+      <c r="Q65">
+        <v>0.2153811199999893</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2838638476596154</v>
+      </c>
+      <c r="T65">
+        <v>4.474703132848788</v>
+      </c>
+      <c r="U65">
+        <v>0.2088</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0.2088</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.5198949229973231</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2382736236340577</v>
+      </c>
+      <c r="C66">
+        <v>-28.24821518762477</v>
+      </c>
+      <c r="D66">
+        <v>110.5445848123753</v>
+      </c>
+      <c r="E66">
+        <v>183.8728</v>
+      </c>
+      <c r="F66">
+        <v>185.2928</v>
+      </c>
+      <c r="G66">
+        <v>46.5</v>
+      </c>
+      <c r="H66">
+        <v>288.1</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>38.3</v>
+      </c>
+      <c r="K66">
+        <v>18.5</v>
+      </c>
+      <c r="L66">
+        <v>19.8</v>
+      </c>
+      <c r="M66">
+        <v>38.68913664000001</v>
+      </c>
+      <c r="N66">
+        <v>-18.88913664000001</v>
+      </c>
+      <c r="O66">
+        <v>-0</v>
+      </c>
+      <c r="P66">
+        <v>-18.88913664000001</v>
+      </c>
+      <c r="Q66">
+        <v>-0.3891366400000109</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2906711767612713</v>
+      </c>
+      <c r="T66">
+        <v>4.599000442094587</v>
+      </c>
+      <c r="U66">
+        <v>0.2088</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0.2088</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.5117715648254899</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2399736236340577</v>
+      </c>
+      <c r="C67">
+        <v>-32.07756247187754</v>
+      </c>
+      <c r="D67">
+        <v>109.6104375281225</v>
+      </c>
+      <c r="E67">
+        <v>186.7680000000001</v>
+      </c>
+      <c r="F67">
+        <v>188.188</v>
+      </c>
+      <c r="G67">
+        <v>46.5</v>
+      </c>
+      <c r="H67">
+        <v>288.1</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>38.3</v>
+      </c>
+      <c r="K67">
+        <v>18.5</v>
+      </c>
+      <c r="L67">
+        <v>19.8</v>
+      </c>
+      <c r="M67">
+        <v>39.29365440000002</v>
+      </c>
+      <c r="N67">
+        <v>-19.49365440000001</v>
+      </c>
+      <c r="O67">
+        <v>-0</v>
+      </c>
+      <c r="P67">
+        <v>-19.49365440000001</v>
+      </c>
+      <c r="Q67">
+        <v>-0.9936544000000183</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2978674960973077</v>
+      </c>
+      <c r="T67">
+        <v>4.730400454725863</v>
+      </c>
+      <c r="U67">
+        <v>0.2088</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0.2088</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.5038981561358669</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2614736236340577</v>
+      </c>
+      <c r="C68">
+        <v>-45.55607435405855</v>
+      </c>
+      <c r="D68">
+        <v>99.02712564594148</v>
+      </c>
+      <c r="E68">
+        <v>189.6632</v>
+      </c>
+      <c r="F68">
+        <v>191.0832</v>
+      </c>
+      <c r="G68">
+        <v>46.5</v>
+      </c>
+      <c r="H68">
+        <v>288.1</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>38.3</v>
+      </c>
+      <c r="K68">
+        <v>18.5</v>
+      </c>
+      <c r="L68">
+        <v>19.8</v>
+      </c>
+      <c r="M68">
+        <v>45.63066816000001</v>
+      </c>
+      <c r="N68">
+        <v>-25.83066816000001</v>
+      </c>
+      <c r="O68">
+        <v>-0</v>
+      </c>
+      <c r="P68">
+        <v>-25.83066816000001</v>
+      </c>
+      <c r="Q68">
+        <v>-7.330668160000016</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.3054871283354638</v>
+      </c>
+      <c r="T68">
+        <v>4.869529879864857</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0.2388</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.4339186954390631</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2634736236340577</v>
+      </c>
+      <c r="C69">
+        <v>-49.33279416972894</v>
+      </c>
+      <c r="D69">
+        <v>98.14560583027112</v>
+      </c>
+      <c r="E69">
+        <v>192.5584000000001</v>
+      </c>
+      <c r="F69">
+        <v>193.9784000000001</v>
+      </c>
+      <c r="G69">
+        <v>46.5</v>
+      </c>
+      <c r="H69">
+        <v>288.1</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>38.3</v>
+      </c>
+      <c r="K69">
+        <v>18.5</v>
+      </c>
+      <c r="L69">
+        <v>19.8</v>
+      </c>
+      <c r="M69">
+        <v>46.32204192000001</v>
+      </c>
+      <c r="N69">
+        <v>-26.52204192000001</v>
+      </c>
+      <c r="O69">
+        <v>-0</v>
+      </c>
+      <c r="P69">
+        <v>-26.52204192000001</v>
+      </c>
+      <c r="Q69">
+        <v>-8.022041920000014</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3135685564668415</v>
+      </c>
+      <c r="T69">
+        <v>5.017091391375915</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>0.2388</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.4274422969996742</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2654736236340577</v>
+      </c>
+      <c r="C70">
+        <v>-53.09395823080305</v>
+      </c>
+      <c r="D70">
+        <v>97.27964176919697</v>
+      </c>
+      <c r="E70">
+        <v>195.4536000000001</v>
+      </c>
+      <c r="F70">
+        <v>196.8736</v>
+      </c>
+      <c r="G70">
+        <v>46.5</v>
+      </c>
+      <c r="H70">
+        <v>288.1</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>38.3</v>
+      </c>
+      <c r="K70">
+        <v>18.5</v>
+      </c>
+      <c r="L70">
+        <v>19.8</v>
+      </c>
+      <c r="M70">
+        <v>47.01341568000001</v>
+      </c>
+      <c r="N70">
+        <v>-27.21341568000001</v>
+      </c>
+      <c r="O70">
+        <v>-0</v>
+      </c>
+      <c r="P70">
+        <v>-27.21341568000001</v>
+      </c>
+      <c r="Q70">
+        <v>-8.713415680000011</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3221550738564303</v>
+      </c>
+      <c r="T70">
+        <v>5.173875497356412</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>0.2388</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.421156380867326</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2674736236340577</v>
+      </c>
+      <c r="C71">
+        <v>-56.83997469335122</v>
+      </c>
+      <c r="D71">
+        <v>96.42882530664883</v>
+      </c>
+      <c r="E71">
+        <v>198.3488000000001</v>
+      </c>
+      <c r="F71">
+        <v>199.7688000000001</v>
+      </c>
+      <c r="G71">
+        <v>46.5</v>
+      </c>
+      <c r="H71">
+        <v>288.1</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>38.3</v>
+      </c>
+      <c r="K71">
+        <v>18.5</v>
+      </c>
+      <c r="L71">
+        <v>19.8</v>
+      </c>
+      <c r="M71">
+        <v>47.70478944000001</v>
+      </c>
+      <c r="N71">
+        <v>-27.90478944000001</v>
+      </c>
+      <c r="O71">
+        <v>-0</v>
+      </c>
+      <c r="P71">
+        <v>-27.90478944000001</v>
+      </c>
+      <c r="Q71">
+        <v>-9.404789440000016</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3312955601098636</v>
+      </c>
+      <c r="T71">
+        <v>5.340774706948554</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>0.2388</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.4150526652025821</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2694736236340577</v>
+      </c>
+      <c r="C72">
+        <v>-60.5712375581686</v>
+      </c>
+      <c r="D72">
+        <v>95.59276244183144</v>
+      </c>
+      <c r="E72">
+        <v>201.2440000000001</v>
+      </c>
+      <c r="F72">
+        <v>202.664</v>
+      </c>
+      <c r="G72">
+        <v>46.5</v>
+      </c>
+      <c r="H72">
+        <v>288.1</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>38.3</v>
+      </c>
+      <c r="K72">
+        <v>18.5</v>
+      </c>
+      <c r="L72">
+        <v>19.8</v>
+      </c>
+      <c r="M72">
+        <v>48.39616320000001</v>
+      </c>
+      <c r="N72">
+        <v>-28.59616320000001</v>
+      </c>
+      <c r="O72">
+        <v>-0</v>
+      </c>
+      <c r="P72">
+        <v>-28.59616320000001</v>
+      </c>
+      <c r="Q72">
+        <v>-10.09616320000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3410454121135256</v>
+      </c>
+      <c r="T72">
+        <v>5.518800530513506</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>0.2388</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.4091233414139739</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2714736236340577</v>
+      </c>
+      <c r="C73">
+        <v>-64.28812727915022</v>
+      </c>
+      <c r="D73">
+        <v>94.77107272084979</v>
+      </c>
+      <c r="E73">
+        <v>204.1392</v>
+      </c>
+      <c r="F73">
+        <v>205.5592</v>
+      </c>
+      <c r="G73">
+        <v>46.5</v>
+      </c>
+      <c r="H73">
+        <v>288.1</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>38.3</v>
+      </c>
+      <c r="K73">
+        <v>18.5</v>
+      </c>
+      <c r="L73">
+        <v>19.8</v>
+      </c>
+      <c r="M73">
+        <v>49.08753696</v>
+      </c>
+      <c r="N73">
+        <v>-29.28753696</v>
+      </c>
+      <c r="O73">
+        <v>-0</v>
+      </c>
+      <c r="P73">
+        <v>-29.28753696</v>
+      </c>
+      <c r="Q73">
+        <v>-10.78753696</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3514676677036472</v>
+      </c>
+      <c r="T73">
+        <v>5.709103997082936</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>0.2388</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.4033610408306785</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2734736236340577</v>
+      </c>
+      <c r="C74">
+        <v>-67.99101134055658</v>
+      </c>
+      <c r="D74">
+        <v>93.96338865944344</v>
+      </c>
+      <c r="E74">
+        <v>207.0344</v>
+      </c>
+      <c r="F74">
+        <v>208.4544</v>
+      </c>
+      <c r="G74">
+        <v>46.5</v>
+      </c>
+      <c r="H74">
+        <v>288.1</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>38.3</v>
+      </c>
+      <c r="K74">
+        <v>18.5</v>
+      </c>
+      <c r="L74">
+        <v>19.8</v>
+      </c>
+      <c r="M74">
+        <v>49.77891072000001</v>
+      </c>
+      <c r="N74">
+        <v>-29.97891072000001</v>
+      </c>
+      <c r="O74">
+        <v>-0</v>
+      </c>
+      <c r="P74">
+        <v>-29.97891072000001</v>
+      </c>
+      <c r="Q74">
+        <v>-11.47891072000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3626343701216345</v>
+      </c>
+      <c r="T74">
+        <v>5.913000568407326</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>0.2388</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3977588041524746</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2754736236340577</v>
+      </c>
+      <c r="C75">
+        <v>-71.68024480500998</v>
+      </c>
+      <c r="D75">
+        <v>93.16935519499003</v>
+      </c>
+      <c r="E75">
+        <v>209.9296</v>
+      </c>
+      <c r="F75">
+        <v>211.3496</v>
+      </c>
+      <c r="G75">
+        <v>46.5</v>
+      </c>
+      <c r="H75">
+        <v>288.1</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>38.3</v>
+      </c>
+      <c r="K75">
+        <v>18.5</v>
+      </c>
+      <c r="L75">
+        <v>19.8</v>
+      </c>
+      <c r="M75">
+        <v>50.47028448</v>
+      </c>
+      <c r="N75">
+        <v>-30.67028448</v>
+      </c>
+      <c r="O75">
+        <v>-0</v>
+      </c>
+      <c r="P75">
+        <v>-30.67028448</v>
+      </c>
+      <c r="Q75">
+        <v>-12.17028448000001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3746282356816951</v>
+      </c>
+      <c r="T75">
+        <v>6.132000589459449</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0.2388</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3923100534106599</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2774736236340577</v>
+      </c>
+      <c r="C76">
+        <v>-75.35617083393925</v>
+      </c>
+      <c r="D76">
+        <v>92.38862916606078</v>
+      </c>
+      <c r="E76">
+        <v>212.8248</v>
+      </c>
+      <c r="F76">
+        <v>214.2448</v>
+      </c>
+      <c r="G76">
+        <v>46.5</v>
+      </c>
+      <c r="H76">
+        <v>288.1</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>38.3</v>
+      </c>
+      <c r="K76">
+        <v>18.5</v>
+      </c>
+      <c r="L76">
+        <v>19.8</v>
+      </c>
+      <c r="M76">
+        <v>51.16165824000001</v>
+      </c>
+      <c r="N76">
+        <v>-31.36165824000001</v>
+      </c>
+      <c r="O76">
+        <v>-0</v>
+      </c>
+      <c r="P76">
+        <v>-31.36165824000001</v>
+      </c>
+      <c r="Q76">
+        <v>-12.86165824000001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3875447062848372</v>
+      </c>
+      <c r="T76">
+        <v>6.367846765977121</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>0.2388</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.3870085662024078</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2794736236340577</v>
+      </c>
+      <c r="C77">
+        <v>-79.01912118207494</v>
+      </c>
+      <c r="D77">
+        <v>91.6208788179251</v>
+      </c>
+      <c r="E77">
+        <v>215.7200000000001</v>
+      </c>
+      <c r="F77">
+        <v>217.14</v>
+      </c>
+      <c r="G77">
+        <v>46.5</v>
+      </c>
+      <c r="H77">
+        <v>288.1</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>38.3</v>
+      </c>
+      <c r="K77">
+        <v>18.5</v>
+      </c>
+      <c r="L77">
+        <v>19.8</v>
+      </c>
+      <c r="M77">
+        <v>51.85303200000001</v>
+      </c>
+      <c r="N77">
+        <v>-32.05303200000002</v>
+      </c>
+      <c r="O77">
+        <v>-0</v>
+      </c>
+      <c r="P77">
+        <v>-32.05303200000002</v>
+      </c>
+      <c r="Q77">
+        <v>-13.55303200000002</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.4014944945362307</v>
+      </c>
+      <c r="T77">
+        <v>6.622560636616206</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0.2388</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3818484519863755</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2814736236340577</v>
+      </c>
+      <c r="C78">
+        <v>-82.66941666749187</v>
+      </c>
+      <c r="D78">
+        <v>90.86578333250814</v>
+      </c>
+      <c r="E78">
+        <v>218.6152</v>
+      </c>
+      <c r="F78">
+        <v>220.0352</v>
+      </c>
+      <c r="G78">
+        <v>46.5</v>
+      </c>
+      <c r="H78">
+        <v>288.1</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>38.3</v>
+      </c>
+      <c r="K78">
+        <v>18.5</v>
+      </c>
+      <c r="L78">
+        <v>19.8</v>
+      </c>
+      <c r="M78">
+        <v>52.54440576000001</v>
+      </c>
+      <c r="N78">
+        <v>-32.74440576000001</v>
+      </c>
+      <c r="O78">
+        <v>-0</v>
+      </c>
+      <c r="P78">
+        <v>-32.74440576000001</v>
+      </c>
+      <c r="Q78">
+        <v>-14.24440576000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.416606765141907</v>
+      </c>
+      <c r="T78">
+        <v>6.898500663141882</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>0.2388</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3768241302497128</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2834736236340577</v>
+      </c>
+      <c r="C79">
+        <v>-86.30736761859899</v>
+      </c>
+      <c r="D79">
+        <v>90.12303238140105</v>
+      </c>
+      <c r="E79">
+        <v>221.5104000000001</v>
+      </c>
+      <c r="F79">
+        <v>222.9304</v>
+      </c>
+      <c r="G79">
+        <v>46.5</v>
+      </c>
+      <c r="H79">
+        <v>288.1</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>38.3</v>
+      </c>
+      <c r="K79">
+        <v>18.5</v>
+      </c>
+      <c r="L79">
+        <v>19.8</v>
+      </c>
+      <c r="M79">
+        <v>53.23577952000002</v>
+      </c>
+      <c r="N79">
+        <v>-33.43577952000001</v>
+      </c>
+      <c r="O79">
+        <v>-0</v>
+      </c>
+      <c r="P79">
+        <v>-33.43577952000001</v>
+      </c>
+      <c r="Q79">
+        <v>-14.93577952000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4330331462350334</v>
+      </c>
+      <c r="T79">
+        <v>7.198435474582833</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <v>0.2388</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3719303103763398</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2854736236340577</v>
+      </c>
+      <c r="C80">
+        <v>-89.93327429938378</v>
+      </c>
+      <c r="D80">
+        <v>89.39232570061624</v>
+      </c>
+      <c r="E80">
+        <v>224.4056</v>
+      </c>
+      <c r="F80">
+        <v>225.8256</v>
+      </c>
+      <c r="G80">
+        <v>46.5</v>
+      </c>
+      <c r="H80">
+        <v>288.1</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>38.3</v>
+      </c>
+      <c r="K80">
+        <v>18.5</v>
+      </c>
+      <c r="L80">
+        <v>19.8</v>
+      </c>
+      <c r="M80">
+        <v>53.92715328000001</v>
+      </c>
+      <c r="N80">
+        <v>-34.12715328000002</v>
+      </c>
+      <c r="O80">
+        <v>-0</v>
+      </c>
+      <c r="P80">
+        <v>-34.12715328000002</v>
+      </c>
+      <c r="Q80">
+        <v>-15.62715328000002</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4509528347002622</v>
+      </c>
+      <c r="T80">
+        <v>7.525637087063871</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>0.2388</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3671619730638226</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2874736236340577</v>
+      </c>
+      <c r="C81">
+        <v>-93.54742731413671</v>
+      </c>
+      <c r="D81">
+        <v>88.67337268586334</v>
+      </c>
+      <c r="E81">
+        <v>227.3008000000001</v>
+      </c>
+      <c r="F81">
+        <v>228.7208000000001</v>
+      </c>
+      <c r="G81">
+        <v>46.5</v>
+      </c>
+      <c r="H81">
+        <v>288.1</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>38.3</v>
+      </c>
+      <c r="K81">
+        <v>18.5</v>
+      </c>
+      <c r="L81">
+        <v>19.8</v>
+      </c>
+      <c r="M81">
+        <v>54.61852704000002</v>
+      </c>
+      <c r="N81">
+        <v>-34.81852704000002</v>
+      </c>
+      <c r="O81">
+        <v>-0</v>
+      </c>
+      <c r="P81">
+        <v>-34.81852704000002</v>
+      </c>
+      <c r="Q81">
+        <v>-16.31852704000002</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4705791601621795</v>
+      </c>
+      <c r="T81">
+        <v>7.884000757876438</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0</v>
+      </c>
+      <c r="W81">
+        <v>0.2388</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3625143531516223</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2894736236340577</v>
+      </c>
+      <c r="C82">
+        <v>-97.15010799280046</v>
+      </c>
+      <c r="D82">
+        <v>87.96589200719959</v>
+      </c>
+      <c r="E82">
+        <v>230.1960000000001</v>
+      </c>
+      <c r="F82">
+        <v>231.616</v>
+      </c>
+      <c r="G82">
+        <v>46.5</v>
+      </c>
+      <c r="H82">
+        <v>288.1</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>38.3</v>
+      </c>
+      <c r="K82">
+        <v>18.5</v>
+      </c>
+      <c r="L82">
+        <v>19.8</v>
+      </c>
+      <c r="M82">
+        <v>55.30990080000002</v>
+      </c>
+      <c r="N82">
+        <v>-35.50990080000001</v>
+      </c>
+      <c r="O82">
+        <v>-0</v>
+      </c>
+      <c r="P82">
+        <v>-35.50990080000001</v>
+      </c>
+      <c r="Q82">
+        <v>-17.00990080000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4921681181702884</v>
+      </c>
+      <c r="T82">
+        <v>8.278200795770259</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0</v>
+      </c>
+      <c r="W82">
+        <v>0.2388</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3579829237372272</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2914736236340577</v>
+      </c>
+      <c r="C83">
+        <v>-100.7415887580188</v>
+      </c>
+      <c r="D83">
+        <v>87.26961124198129</v>
+      </c>
+      <c r="E83">
+        <v>233.0912000000001</v>
+      </c>
+      <c r="F83">
+        <v>234.5112000000001</v>
+      </c>
+      <c r="G83">
+        <v>46.5</v>
+      </c>
+      <c r="H83">
+        <v>288.1</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>38.3</v>
+      </c>
+      <c r="K83">
+        <v>18.5</v>
+      </c>
+      <c r="L83">
+        <v>19.8</v>
+      </c>
+      <c r="M83">
+        <v>56.00127456000002</v>
+      </c>
+      <c r="N83">
+        <v>-36.20127456000002</v>
+      </c>
+      <c r="O83">
+        <v>-0</v>
+      </c>
+      <c r="P83">
+        <v>-36.20127456000002</v>
+      </c>
+      <c r="Q83">
+        <v>-17.70127456000002</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.516029598073988</v>
+      </c>
+      <c r="T83">
+        <v>8.713895574495011</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83">
+        <v>0.2388</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3535633814688663</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2934736236340577</v>
+      </c>
+      <c r="C84">
+        <v>-104.3221334748896</v>
+      </c>
+      <c r="D84">
+        <v>86.58426652511042</v>
+      </c>
+      <c r="E84">
+        <v>235.9864000000001</v>
+      </c>
+      <c r="F84">
+        <v>237.4064</v>
+      </c>
+      <c r="G84">
+        <v>46.5</v>
+      </c>
+      <c r="H84">
+        <v>288.1</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>38.3</v>
+      </c>
+      <c r="K84">
+        <v>18.5</v>
+      </c>
+      <c r="L84">
+        <v>19.8</v>
+      </c>
+      <c r="M84">
+        <v>56.69264832000002</v>
+      </c>
+      <c r="N84">
+        <v>-36.89264832000002</v>
+      </c>
+      <c r="O84">
+        <v>-0</v>
+      </c>
+      <c r="P84">
+        <v>-36.89264832000002</v>
+      </c>
+      <c r="Q84">
+        <v>-18.39264832000002</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5425423535225429</v>
+      </c>
+      <c r="T84">
+        <v>9.198000884189177</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <v>0.2388</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3492516329143678</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2954736236340577</v>
+      </c>
+      <c r="C85">
+        <v>-107.8919977843674</v>
+      </c>
+      <c r="D85">
+        <v>85.90960221563269</v>
+      </c>
+      <c r="E85">
+        <v>238.8816000000001</v>
+      </c>
+      <c r="F85">
+        <v>240.3016000000001</v>
+      </c>
+      <c r="G85">
+        <v>46.5</v>
+      </c>
+      <c r="H85">
+        <v>288.1</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>38.3</v>
+      </c>
+      <c r="K85">
+        <v>18.5</v>
+      </c>
+      <c r="L85">
+        <v>19.8</v>
+      </c>
+      <c r="M85">
+        <v>57.38402208000002</v>
+      </c>
+      <c r="N85">
+        <v>-37.58402208000001</v>
+      </c>
+      <c r="O85">
+        <v>-0</v>
+      </c>
+      <c r="P85">
+        <v>-37.58402208000001</v>
+      </c>
+      <c r="Q85">
+        <v>-19.08402208000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5721742566709278</v>
+      </c>
+      <c r="T85">
+        <v>9.739059759729718</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0</v>
+      </c>
+      <c r="W85">
+        <v>0.2388</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.3450437819153996</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2974736236340577</v>
+      </c>
+      <c r="C86">
+        <v>-111.4514294211976</v>
+      </c>
+      <c r="D86">
+        <v>85.24537057880244</v>
+      </c>
+      <c r="E86">
+        <v>241.7768</v>
+      </c>
+      <c r="F86">
+        <v>243.1968</v>
+      </c>
+      <c r="G86">
+        <v>46.5</v>
+      </c>
+      <c r="H86">
+        <v>288.1</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>38.3</v>
+      </c>
+      <c r="K86">
+        <v>18.5</v>
+      </c>
+      <c r="L86">
+        <v>19.8</v>
+      </c>
+      <c r="M86">
+        <v>58.07539584000001</v>
+      </c>
+      <c r="N86">
+        <v>-38.27539584</v>
+      </c>
+      <c r="O86">
+        <v>-0</v>
+      </c>
+      <c r="P86">
+        <v>-38.27539584</v>
+      </c>
+      <c r="Q86">
+        <v>-19.77539584000001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.6055101477128604</v>
+      </c>
+      <c r="T86">
+        <v>10.34775099471282</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0</v>
+      </c>
+      <c r="W86">
+        <v>0.2388</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3409361178449783</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2994736236340577</v>
+      </c>
+      <c r="C87">
+        <v>-115.0006685172166</v>
+      </c>
+      <c r="D87">
+        <v>84.59133148278345</v>
+      </c>
+      <c r="E87">
+        <v>244.672</v>
+      </c>
+      <c r="F87">
+        <v>246.092</v>
+      </c>
+      <c r="G87">
+        <v>46.5</v>
+      </c>
+      <c r="H87">
+        <v>288.1</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>38.3</v>
+      </c>
+      <c r="K87">
+        <v>18.5</v>
+      </c>
+      <c r="L87">
+        <v>19.8</v>
+      </c>
+      <c r="M87">
+        <v>58.7667696</v>
+      </c>
+      <c r="N87">
+        <v>-38.96676960000001</v>
+      </c>
+      <c r="O87">
+        <v>-0</v>
+      </c>
+      <c r="P87">
+        <v>-38.96676960000001</v>
+      </c>
+      <c r="Q87">
+        <v>-20.46676960000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.6432908242270512</v>
+      </c>
+      <c r="T87">
+        <v>11.03760106102701</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <v>0.2388</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3369251046938608</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3014736236340577</v>
+      </c>
+      <c r="C88">
+        <v>-118.5399478907941</v>
+      </c>
+      <c r="D88">
+        <v>83.94725210920595</v>
+      </c>
+      <c r="E88">
+        <v>247.5672</v>
+      </c>
+      <c r="F88">
+        <v>248.9872</v>
+      </c>
+      <c r="G88">
+        <v>46.5</v>
+      </c>
+      <c r="H88">
+        <v>288.1</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>38.3</v>
+      </c>
+      <c r="K88">
+        <v>18.5</v>
+      </c>
+      <c r="L88">
+        <v>19.8</v>
+      </c>
+      <c r="M88">
+        <v>59.45814336000001</v>
+      </c>
+      <c r="N88">
+        <v>-39.65814336000001</v>
+      </c>
+      <c r="O88">
+        <v>-0</v>
+      </c>
+      <c r="P88">
+        <v>-39.65814336000001</v>
+      </c>
+      <c r="Q88">
+        <v>-21.15814336000001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.686468740243269</v>
+      </c>
+      <c r="T88">
+        <v>11.82600113681465</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0</v>
+      </c>
+      <c r="W88">
+        <v>0.2388</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3330073709183508</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3034736236340577</v>
+      </c>
+      <c r="C89">
+        <v>-122.069493323154</v>
+      </c>
+      <c r="D89">
+        <v>83.31290667684601</v>
+      </c>
+      <c r="E89">
+        <v>250.4624</v>
+      </c>
+      <c r="F89">
+        <v>251.8824</v>
+      </c>
+      <c r="G89">
+        <v>46.5</v>
+      </c>
+      <c r="H89">
+        <v>288.1</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>38.3</v>
+      </c>
+      <c r="K89">
+        <v>18.5</v>
+      </c>
+      <c r="L89">
+        <v>19.8</v>
+      </c>
+      <c r="M89">
+        <v>60.14951712000001</v>
+      </c>
+      <c r="N89">
+        <v>-40.34951712</v>
+      </c>
+      <c r="O89">
+        <v>-0</v>
+      </c>
+      <c r="P89">
+        <v>-40.34951712</v>
+      </c>
+      <c r="Q89">
+        <v>-21.84951712000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.7362894125696744</v>
+      </c>
+      <c r="T89">
+        <v>12.73569353195424</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0</v>
+      </c>
+      <c r="W89">
+        <v>0.2388</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.3291796999882549</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3054736236340577</v>
+      </c>
+      <c r="C90">
+        <v>-125.5895238222601</v>
+      </c>
+      <c r="D90">
+        <v>82.68807617773992</v>
+      </c>
+      <c r="E90">
+        <v>253.3576</v>
+      </c>
+      <c r="F90">
+        <v>254.7776</v>
+      </c>
+      <c r="G90">
+        <v>46.5</v>
+      </c>
+      <c r="H90">
+        <v>288.1</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>38.3</v>
+      </c>
+      <c r="K90">
+        <v>18.5</v>
+      </c>
+      <c r="L90">
+        <v>19.8</v>
+      </c>
+      <c r="M90">
+        <v>60.84089088000001</v>
+      </c>
+      <c r="N90">
+        <v>-41.04089088000001</v>
+      </c>
+      <c r="O90">
+        <v>-0</v>
+      </c>
+      <c r="P90">
+        <v>-41.04089088000001</v>
+      </c>
+      <c r="Q90">
+        <v>-22.54089088000001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.794413530283814</v>
+      </c>
+      <c r="T90">
+        <v>13.79700132628376</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0</v>
+      </c>
+      <c r="W90">
+        <v>0.2388</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3254390215792975</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3074736236340577</v>
+      </c>
+      <c r="C91">
+        <v>-129.100251874916</v>
+      </c>
+      <c r="D91">
+        <v>82.07254812508403</v>
+      </c>
+      <c r="E91">
+        <v>256.2528</v>
+      </c>
+      <c r="F91">
+        <v>257.6728000000001</v>
+      </c>
+      <c r="G91">
+        <v>46.5</v>
+      </c>
+      <c r="H91">
+        <v>288.1</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>38.3</v>
+      </c>
+      <c r="K91">
+        <v>18.5</v>
+      </c>
+      <c r="L91">
+        <v>19.8</v>
+      </c>
+      <c r="M91">
+        <v>61.53226464000002</v>
+      </c>
+      <c r="N91">
+        <v>-41.73226464000001</v>
+      </c>
+      <c r="O91">
+        <v>-0</v>
+      </c>
+      <c r="P91">
+        <v>-41.73226464000001</v>
+      </c>
+      <c r="Q91">
+        <v>-23.23226464000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.8631056694005244</v>
+      </c>
+      <c r="T91">
+        <v>15.05127417412774</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0</v>
+      </c>
+      <c r="W91">
+        <v>0.2388</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.3217824033593053</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3094736236340577</v>
+      </c>
+      <c r="C92">
+        <v>-132.6018836876887</v>
+      </c>
+      <c r="D92">
+        <v>81.4661163123113</v>
+      </c>
+      <c r="E92">
+        <v>259.148</v>
+      </c>
+      <c r="F92">
+        <v>260.568</v>
+      </c>
+      <c r="G92">
+        <v>46.5</v>
+      </c>
+      <c r="H92">
+        <v>288.1</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>38.3</v>
+      </c>
+      <c r="K92">
+        <v>18.5</v>
+      </c>
+      <c r="L92">
+        <v>19.8</v>
+      </c>
+      <c r="M92">
+        <v>62.22363840000001</v>
+      </c>
+      <c r="N92">
+        <v>-42.42363840000002</v>
+      </c>
+      <c r="O92">
+        <v>-0</v>
+      </c>
+      <c r="P92">
+        <v>-42.42363840000002</v>
+      </c>
+      <c r="Q92">
+        <v>-23.92363840000002</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.9455362363405768</v>
+      </c>
+      <c r="T92">
+        <v>16.55640159154052</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0</v>
+      </c>
+      <c r="W92">
+        <v>0.2388</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.3182070433219796</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3114736236340577</v>
+      </c>
+      <c r="C93">
+        <v>-136.0946194172292</v>
+      </c>
+      <c r="D93">
+        <v>80.86858058277079</v>
+      </c>
+      <c r="E93">
+        <v>262.0432</v>
+      </c>
+      <c r="F93">
+        <v>263.4632</v>
+      </c>
+      <c r="G93">
+        <v>46.5</v>
+      </c>
+      <c r="H93">
+        <v>288.1</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>38.3</v>
+      </c>
+      <c r="K93">
+        <v>18.5</v>
+      </c>
+      <c r="L93">
+        <v>19.8</v>
+      </c>
+      <c r="M93">
+        <v>62.91501216000001</v>
+      </c>
+      <c r="N93">
+        <v>-43.11501216000001</v>
+      </c>
+      <c r="O93">
+        <v>-0</v>
+      </c>
+      <c r="P93">
+        <v>-43.11501216000001</v>
+      </c>
+      <c r="Q93">
+        <v>-24.61501216000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.046284707045086</v>
+      </c>
+      <c r="T93">
+        <v>18.39600176837835</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0</v>
+      </c>
+      <c r="W93">
+        <v>0.2388</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.3147102626261338</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3134736236340577</v>
+      </c>
+      <c r="C94">
+        <v>-139.5786533905307</v>
+      </c>
+      <c r="D94">
+        <v>80.27974660946938</v>
+      </c>
+      <c r="E94">
+        <v>264.9384000000001</v>
+      </c>
+      <c r="F94">
+        <v>266.3584000000001</v>
+      </c>
+      <c r="G94">
+        <v>46.5</v>
+      </c>
+      <c r="H94">
+        <v>288.1</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>38.3</v>
+      </c>
+      <c r="K94">
+        <v>18.5</v>
+      </c>
+      <c r="L94">
+        <v>19.8</v>
+      </c>
+      <c r="M94">
+        <v>63.60638592000002</v>
+      </c>
+      <c r="N94">
+        <v>-43.80638592000003</v>
+      </c>
+      <c r="O94">
+        <v>-0</v>
+      </c>
+      <c r="P94">
+        <v>-43.80638592000003</v>
+      </c>
+      <c r="Q94">
+        <v>-25.30638592000003</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.172220295425721</v>
+      </c>
+      <c r="T94">
+        <v>20.69550198942565</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0</v>
+      </c>
+      <c r="W94">
+        <v>0.2388</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3112894989019365</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3154736236340577</v>
+      </c>
+      <c r="C95">
+        <v>-143.0541743156338</v>
+      </c>
+      <c r="D95">
+        <v>79.6994256843663</v>
+      </c>
+      <c r="E95">
+        <v>267.8336</v>
+      </c>
+      <c r="F95">
+        <v>269.2536000000001</v>
+      </c>
+      <c r="G95">
+        <v>46.5</v>
+      </c>
+      <c r="H95">
+        <v>288.1</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>38.3</v>
+      </c>
+      <c r="K95">
+        <v>18.5</v>
+      </c>
+      <c r="L95">
+        <v>19.8</v>
+      </c>
+      <c r="M95">
+        <v>64.29775968000001</v>
+      </c>
+      <c r="N95">
+        <v>-44.49775968000002</v>
+      </c>
+      <c r="O95">
+        <v>-0</v>
+      </c>
+      <c r="P95">
+        <v>-44.49775968000002</v>
+      </c>
+      <c r="Q95">
+        <v>-25.99775968000002</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.334137480486539</v>
+      </c>
+      <c r="T95">
+        <v>23.65200227362932</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0</v>
+      </c>
+      <c r="W95">
+        <v>0.2388</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3079422999890125</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3174736236340577</v>
+      </c>
+      <c r="C96">
+        <v>-146.5213654832588</v>
+      </c>
+      <c r="D96">
+        <v>79.1274345167413</v>
+      </c>
+      <c r="E96">
+        <v>270.7288</v>
+      </c>
+      <c r="F96">
+        <v>272.1488000000001</v>
+      </c>
+      <c r="G96">
+        <v>46.5</v>
+      </c>
+      <c r="H96">
+        <v>288.1</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>38.3</v>
+      </c>
+      <c r="K96">
+        <v>18.5</v>
+      </c>
+      <c r="L96">
+        <v>19.8</v>
+      </c>
+      <c r="M96">
+        <v>64.98913344000002</v>
+      </c>
+      <c r="N96">
+        <v>-45.18913344000002</v>
+      </c>
+      <c r="O96">
+        <v>-0</v>
+      </c>
+      <c r="P96">
+        <v>-45.18913344000002</v>
+      </c>
+      <c r="Q96">
+        <v>-26.68913344000002</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.550027060567629</v>
+      </c>
+      <c r="T96">
+        <v>27.59400265256755</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0</v>
+      </c>
+      <c r="W96">
+        <v>0.2388</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.3046663180742357</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3194736236340577</v>
+      </c>
+      <c r="C97">
+        <v>-149.9804049598168</v>
+      </c>
+      <c r="D97">
+        <v>78.56359504018323</v>
+      </c>
+      <c r="E97">
+        <v>273.624</v>
+      </c>
+      <c r="F97">
+        <v>275.044</v>
+      </c>
+      <c r="G97">
+        <v>46.5</v>
+      </c>
+      <c r="H97">
+        <v>288.1</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>38.3</v>
+      </c>
+      <c r="K97">
+        <v>18.5</v>
+      </c>
+      <c r="L97">
+        <v>19.8</v>
+      </c>
+      <c r="M97">
+        <v>65.68050720000001</v>
+      </c>
+      <c r="N97">
+        <v>-45.88050720000001</v>
+      </c>
+      <c r="O97">
+        <v>-0</v>
+      </c>
+      <c r="P97">
+        <v>-45.88050720000001</v>
+      </c>
+      <c r="Q97">
+        <v>-27.38050720000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.852272472681156</v>
+      </c>
+      <c r="T97">
+        <v>33.11280318308108</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0</v>
+      </c>
+      <c r="W97">
+        <v>0.2388</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.3014593041997702</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3214736236340577</v>
+      </c>
+      <c r="C98">
+        <v>-153.4314657722277</v>
+      </c>
+      <c r="D98">
+        <v>78.00773422777232</v>
+      </c>
+      <c r="E98">
+        <v>276.5192</v>
+      </c>
+      <c r="F98">
+        <v>277.9392</v>
+      </c>
+      <c r="G98">
+        <v>46.5</v>
+      </c>
+      <c r="H98">
+        <v>288.1</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>38.3</v>
+      </c>
+      <c r="K98">
+        <v>18.5</v>
+      </c>
+      <c r="L98">
+        <v>19.8</v>
+      </c>
+      <c r="M98">
+        <v>66.37188096000001</v>
+      </c>
+      <c r="N98">
+        <v>-46.57188096000002</v>
+      </c>
+      <c r="O98">
+        <v>-0</v>
+      </c>
+      <c r="P98">
+        <v>-46.57188096000002</v>
+      </c>
+      <c r="Q98">
+        <v>-28.07188096000002</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.30564059085144</v>
+      </c>
+      <c r="T98">
+        <v>41.39100397885125</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0</v>
+      </c>
+      <c r="W98">
+        <v>0.2388</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2983191031143558</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3234736236340577</v>
+      </c>
+      <c r="C99">
+        <v>-156.8747160849468</v>
+      </c>
+      <c r="D99">
+        <v>77.45968391505316</v>
+      </c>
+      <c r="E99">
+        <v>279.4144</v>
+      </c>
+      <c r="F99">
+        <v>280.8344</v>
+      </c>
+      <c r="G99">
+        <v>46.5</v>
+      </c>
+      <c r="H99">
+        <v>288.1</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>38.3</v>
+      </c>
+      <c r="K99">
+        <v>18.5</v>
+      </c>
+      <c r="L99">
+        <v>19.8</v>
+      </c>
+      <c r="M99">
+        <v>67.06325472</v>
+      </c>
+      <c r="N99">
+        <v>-47.26325472000001</v>
+      </c>
+      <c r="O99">
+        <v>-0</v>
+      </c>
+      <c r="P99">
+        <v>-47.26325472000001</v>
+      </c>
+      <c r="Q99">
+        <v>-28.76325472000001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.061254121135254</v>
+      </c>
+      <c r="T99">
+        <v>55.18800530513501</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0</v>
+      </c>
+      <c r="W99">
+        <v>0.2388</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2952436484430739</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3254736236340577</v>
+      </c>
+      <c r="C100">
+        <v>-160.310319369582</v>
+      </c>
+      <c r="D100">
+        <v>76.919280630418</v>
+      </c>
+      <c r="E100">
+        <v>282.3096</v>
+      </c>
+      <c r="F100">
+        <v>283.7296</v>
+      </c>
+      <c r="G100">
+        <v>46.5</v>
+      </c>
+      <c r="H100">
+        <v>288.1</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>38.3</v>
+      </c>
+      <c r="K100">
+        <v>18.5</v>
+      </c>
+      <c r="L100">
+        <v>19.8</v>
+      </c>
+      <c r="M100">
+        <v>67.75462848000001</v>
+      </c>
+      <c r="N100">
+        <v>-47.95462848000001</v>
+      </c>
+      <c r="O100">
+        <v>-0</v>
+      </c>
+      <c r="P100">
+        <v>-47.95462848000001</v>
+      </c>
+      <c r="Q100">
+        <v>-29.45462848000001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.57248118170288</v>
+      </c>
+      <c r="T100">
+        <v>82.7820079577025</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0</v>
+      </c>
+      <c r="W100">
+        <v>0.2388</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2922309581528384</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3274736236340577</v>
+      </c>
+      <c r="C101">
+        <v>-163.7384345674591</v>
+      </c>
+      <c r="D101">
+        <v>76.38636543254091</v>
+      </c>
+      <c r="E101">
+        <v>285.2048</v>
+      </c>
+      <c r="F101">
+        <v>286.6248000000001</v>
+      </c>
+      <c r="G101">
+        <v>46.5</v>
+      </c>
+      <c r="H101">
+        <v>288.1</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>38.3</v>
+      </c>
+      <c r="K101">
+        <v>18.5</v>
+      </c>
+      <c r="L101">
+        <v>19.8</v>
+      </c>
+      <c r="M101">
+        <v>68.44600224000001</v>
+      </c>
+      <c r="N101">
+        <v>-48.64600224000002</v>
+      </c>
+      <c r="O101">
+        <v>-0</v>
+      </c>
+      <c r="P101">
+        <v>-48.64600224000002</v>
+      </c>
+      <c r="Q101">
+        <v>-30.14600224000002</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>9.10616236340576</v>
+      </c>
+      <c r="T101">
+        <v>165.564015915405</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0</v>
+      </c>
+      <c r="W101">
+        <v>0.2388</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2892791302927087</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
